--- a/tame_output/ON/bt/strategyON_20240529.xlsx
+++ b/tame_output/ON/bt/strategyON_20240529.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>17.0%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.4%</t>
+          <t>443.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-626.4%</t>
+          <t>-640.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-29.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.2%</t>
+          <t>-286.0%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-248.8%</t>
+          <t>-249.1%</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-178.9%</t>
+          <t>-179.1%</t>
         </is>
       </c>
     </row>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.624165904152432</v>
+        <v>-4.765327323016313</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9689496462028844</v>
+        <v>0.9124850786573317</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3532524087299551</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.537922441126054</v>
+        <v>-4.679083859989936</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9983933019872959</v>
+        <v>0.9419287344417433</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3532524087299551</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.583229260525034</v>
+        <v>-4.724390679388915</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9720463496722296</v>
+        <v>0.9155817821266767</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3940625717391859</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.460101553530951</v>
+        <v>-4.601262972394832</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.021849305502964</v>
+        <v>0.9653847379574116</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3940625717391859</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.367291072080091</v>
+        <v>-4.508452490943973</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9882461899746737</v>
+        <v>0.9317816224291211</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3012520902883266</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.318728019859061</v>
+        <v>-4.459889438722943</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.009544886787687</v>
+        <v>0.953080319242134</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.2526890380672964</v>
@@ -46355,10 +46355,10 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.206056801622811</v>
+        <v>-4.347218220486693</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.04968908259391</v>
+        <v>0.993224515048357</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.1400178198310462</v>
@@ -46378,10 +46378,10 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.093679800440138</v>
+        <v>-4.23484121930402</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.100131178897646</v>
+        <v>1.043666611352093</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.1400178198310462</v>
@@ -46401,10 +46401,10 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.291914369326869</v>
+        <v>-4.433075788190751</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.032334553111493</v>
+        <v>0.9758699855659401</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.3382523887177767</v>
@@ -46424,10 +46424,10 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.374915650352148</v>
+        <v>-4.516077069216029</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8374897607020344</v>
+        <v>0.7810251931564818</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.3568232732449505</v>
@@ -46447,10 +46447,10 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.501982656659136</v>
+        <v>-4.643144075523018</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9068126188984449</v>
+        <v>0.8503480513528923</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.3568232732449505</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.588581239640239</v>
+        <v>-4.72974265850412</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8866862118083267</v>
+        <v>0.8302216442627741</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.3568232732449505</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.550197577082088</v>
+        <v>-4.691358995945969</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8994591181739557</v>
+        <v>0.8429945506284031</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.3184396106867993</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.373081247046922</v>
+        <v>-4.514242665910803</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9670346790333242</v>
+        <v>0.9105701114877716</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.3184396106867993</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.343379123070628</v>
+        <v>-4.48454054193451</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9795989203857547</v>
+        <v>0.9231343528402021</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.3229097359021127</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.16400370183186</v>
+        <v>-4.305165120695742</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.045136064187676</v>
+        <v>0.9886714966421235</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.166132977731394</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.209017915352467</v>
+        <v>-4.350179334216348</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.007937834111023</v>
+        <v>0.951473266565471</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1964818730459986</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.476022425624902</v>
+        <v>-4.617183844488783</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.906827592340995</v>
+        <v>0.8503630247954428</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3908449110889472</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.577220207062075</v>
+        <v>-4.718381625925955</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8655524016626273</v>
+        <v>0.8090878341170751</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4592537246342664</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.544744620891302</v>
+        <v>-4.685906039755183</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.876142597685253</v>
+        <v>0.8196780301397006</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4592537246342664</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.525706493184005</v>
+        <v>-4.666867912047886</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8802825679764168</v>
+        <v>0.8238180004308644</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.5174373359654609</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.556833124334624</v>
+        <v>-4.697994543198504</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.04541378445485</v>
+        <v>0.9889492169092977</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.5174373359654609</v>
@@ -46723,10 +46723,10 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.609153504935415</v>
+        <v>-4.750314923799296</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.025318961200667</v>
+        <v>0.9688543936551146</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4824904759565888</v>
@@ -46746,10 +46746,10 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.753476410860334</v>
+        <v>-4.894637829724215</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9735983292276251</v>
+        <v>0.9171337616820729</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4824904759565888</v>
@@ -46769,10 +46769,10 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.605733440625332</v>
+        <v>-4.746894859489212</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.111848165113648</v>
+        <v>1.055383597568096</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.3146831187217056</v>
@@ -46792,10 +46792,10 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.707748123156553</v>
+        <v>-4.848909542020434</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.073835913632641</v>
+        <v>1.017371346087088</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.3146831187217056</v>
@@ -46815,10 +46815,10 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.57113877906246</v>
+        <v>-4.712300197926341</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.129141999661936</v>
+        <v>1.072677432116384</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.1780737746276131</v>
@@ -46838,10 +46838,10 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.71390411188511</v>
+        <v>-4.855065530748991</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.071116343272986</v>
+        <v>1.014651775727434</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.3208391074502636</v>
@@ -46861,10 +46861,10 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.651606113108988</v>
+        <v>-4.792767531972869</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.162371096580256</v>
+        <v>1.105906529034704</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.3208391074502636</v>
@@ -46884,10 +46884,10 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.44981591544383</v>
+        <v>-4.590977334307711</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9516680480357174</v>
+        <v>0.895203480490165</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.1228209152811092</v>
@@ -46907,10 +46907,10 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.389925233801237</v>
+        <v>-4.531086652665118</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.04591455301493</v>
+        <v>0.9894499854693775</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.06293023363851569</v>
@@ -46930,10 +46930,10 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.487665778426211</v>
+        <v>-4.628827197290092</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.021446071280984</v>
+        <v>0.9649815037354315</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.07881951177149588</v>
@@ -46953,10 +46953,10 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.664003538549141</v>
+        <v>-4.805164957413021</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9494469480564836</v>
+        <v>0.8929823805109314</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2551572718944253</v>
@@ -46976,10 +46976,10 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.663314166387917</v>
+        <v>-4.804475585251798</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9482143149609015</v>
+        <v>0.8917497474153491</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2551572718944253</v>
@@ -46999,10 +46999,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.66988513144251</v>
+        <v>-4.811046550306391</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9454487963745006</v>
+        <v>0.8889842288289482</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.2617282369490182</v>
@@ -47022,10 +47022,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.661931161147738</v>
+        <v>-4.803092580011619</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9486303844924096</v>
+        <v>0.8921658169468571</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.2617282369490182</v>
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.792576436747339</v>
+        <v>3.451202335531033</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.648763682804894</v>
+        <v>-4.792719203678532</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9602791328573517</v>
+        <v>0.9026969245078966</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.2485607586061747</v>
+        <v>-0.2513548606159309</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.671004575129352</v>
+        <v>2.669328113923498</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240529.xlsx
+++ b/tame_output/ON/bt/strategyON_20240529.xlsx
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831153</v>
+        <v>3.320996253831154</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.31188830135569</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279815</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386095</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757925</v>
+        <v>3.293490533757924</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760743</v>
+        <v>3.293766719760742</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706673</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201489</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495497</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006528</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309419</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330517</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108633</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309411</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937496</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410274</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322546</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311945</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097239</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017767</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839721</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388724</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626469</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291808</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710808</v>
+        <v>3.760333686710809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409202</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245367891991</v>
+        <v>3.812453678919909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318095</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988307</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074778</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.79769488424229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367679</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232699787996</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003597</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417698</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205893</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.77321029711129</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264159</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742295</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316043</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170532</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729265</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190763</v>
+        <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913419</v>
+        <v>3.741174069913421</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.75114719753248</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793896</v>
+        <v>3.741328448793898</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011229</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982224</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509531</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760806</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815452</v>
+        <v>3.705571661815454</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789119</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519904</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394724</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992185</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785242</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319541</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397789</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024957</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863221</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.451202335531033</v>
+        <v>3.451202335531035</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>

--- a/tame_output/ON/bt/strategyON_20240529.xlsx
+++ b/tame_output/ON/bt/strategyON_20240529.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-51.8%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>127.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>443.8%</t>
+          <t>443.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-640.8%</t>
+          <t>-641.5%</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-286.0%</t>
+          <t>-286.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,11 +1247,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-249.1%</t>
+          <t>-250.2%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-179.1%</t>
+          <t>-186.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1978"/>
+  <dimension ref="A1:G1979"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.31188830135569</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386095</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998563</v>
+        <v>3.367370539998562</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082127</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410274</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.75388257196099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987901</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710809</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919909</v>
+        <v>3.812453678919911</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057528</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674517</v>
+        <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.765327323016313</v>
+        <v>-4.760703407736505</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9124850786573317</v>
+        <v>0.9143346447692551</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3532524087299551</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.679083859989936</v>
+        <v>-4.674459944710128</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9419287344417433</v>
+        <v>0.9437783005536664</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3532524087299551</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.724390679388915</v>
+        <v>-4.719766764109107</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9155817821266767</v>
+        <v>0.9174313482386001</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3940625717391859</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.75357116580319</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.601262972394832</v>
+        <v>-4.596639057115024</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9653847379574116</v>
+        <v>0.9672343040693347</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3940625717391859</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.508452490943973</v>
+        <v>-4.503828575664165</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9317816224291211</v>
+        <v>0.9336311885410442</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3012520902883266</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.459889438722943</v>
+        <v>-4.455265523443135</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.953080319242134</v>
+        <v>0.9549298853540571</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.2526890380672964</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.347218220486693</v>
+        <v>-4.342594305206885</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.993224515048357</v>
+        <v>0.9950740811602801</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.1400178198310462</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.23484121930402</v>
+        <v>-4.230217304024212</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.043666611352093</v>
+        <v>1.045516177464016</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.1400178198310462</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.433075788190751</v>
+        <v>-4.428451872910943</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9758699855659401</v>
+        <v>0.9777195516778634</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.3382523887177767</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.516077069216029</v>
+        <v>-4.511453153936221</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7810251931564818</v>
+        <v>0.7828747592684051</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.3568232732449505</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.643144075523018</v>
+        <v>-4.63852016024321</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8503480513528923</v>
+        <v>0.8521976174648154</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.3568232732449505</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.72974265850412</v>
+        <v>-4.725118743224312</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8302216442627741</v>
+        <v>0.8320712103746972</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.3568232732449505</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913421</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.691358995945969</v>
+        <v>-4.686735080666161</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8429945506284031</v>
+        <v>0.8448441167403264</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.3184396106867993</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.514242665910803</v>
+        <v>-4.509618750630995</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9105701114877716</v>
+        <v>0.9124196775996947</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.3184396106867993</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793898</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.48454054193451</v>
+        <v>-4.479916626654702</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9231343528402021</v>
+        <v>0.9249839189521252</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.3229097359021127</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.305165120695742</v>
+        <v>-4.300541205415934</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9886714966421235</v>
+        <v>0.9905210627540466</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.166132977731394</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.350179334216348</v>
+        <v>-4.34555541893654</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.951473266565471</v>
+        <v>0.9533228326773941</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1964818730459986</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.617183844488783</v>
+        <v>-4.612559929208975</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8503630247954428</v>
+        <v>0.8522125909073659</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3908449110889472</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.718381625925955</v>
+        <v>-4.713757710646147</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8090878341170751</v>
+        <v>0.8109374002289982</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4592537246342664</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815454</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.685906039755183</v>
+        <v>-4.681282124475375</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8196780301397006</v>
+        <v>0.8215275962516237</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4592537246342664</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.666867912047886</v>
+        <v>-4.662243996768078</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8238180004308644</v>
+        <v>0.8256675665427877</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.5174373359654609</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.697994543198504</v>
+        <v>-4.693370627918696</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9889492169092977</v>
+        <v>0.9907987830212208</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.5174373359654609</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.750314923799296</v>
+        <v>-4.745691008519488</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9688543936551146</v>
+        <v>0.9707039597670377</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4824904759565888</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.894637829724215</v>
+        <v>-4.890013914444407</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9171337616820729</v>
+        <v>0.9189833277939961</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4824904759565888</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.746894859489212</v>
+        <v>-4.742270944209404</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.055383597568096</v>
+        <v>1.057233163680019</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.3146831187217056</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.848909542020434</v>
+        <v>-4.844285626740626</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.017371346087088</v>
+        <v>1.019220912199011</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.3146831187217056</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.712300197926341</v>
+        <v>-4.707676282646533</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.072677432116384</v>
+        <v>1.074526998228307</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.1780737746276131</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.855065530748991</v>
+        <v>-4.850441615469183</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.014651775727434</v>
+        <v>1.016501341839357</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.3208391074502636</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.792767531972869</v>
+        <v>-4.788143616693061</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.105906529034704</v>
+        <v>1.107756095146627</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.3208391074502636</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.590977334307711</v>
+        <v>-4.586353419027903</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.895203480490165</v>
+        <v>0.8970530466020881</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.1228209152811092</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.531086652665118</v>
+        <v>-4.52646273738531</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9894499854693775</v>
+        <v>0.9912995515813008</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.06293023363851569</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.628827197290092</v>
+        <v>-4.624203282010284</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9649815037354315</v>
+        <v>0.9668310698473546</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.07881951177149588</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.805164957413021</v>
+        <v>-4.800541042133213</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8929823805109314</v>
+        <v>0.8948319466228545</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2551572718944253</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.804475585251798</v>
+        <v>-4.79985166997199</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8917497474153491</v>
+        <v>0.8935993135272724</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2551572718944253</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.811046550306391</v>
+        <v>-4.806422635026583</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8889842288289482</v>
+        <v>0.8908337949408716</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.2617282369490182</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.803092580011619</v>
+        <v>-4.798468664731811</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8921658169468571</v>
+        <v>0.8940153830587803</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.2617282369490182</v>
@@ -47039,22 +47039,45 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.451202335531035</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.792719203678532</v>
+        <v>-4.799275307550477</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9026969245078966</v>
+        <v>0.9000744829591183</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.2513548606159309</v>
+        <v>-0.2625348797676849</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.669328113923498</v>
+        <v>2.662620102432446</v>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" s="2" t="n">
+        <v>45441</v>
+      </c>
+      <c r="B1979" t="n">
+        <v>3.455524524033331</v>
+      </c>
+      <c r="C1979" t="n">
+        <v>2.597968705899928</v>
+      </c>
+      <c r="D1979" t="n">
+        <v>-4.799275307550477</v>
+      </c>
+      <c r="E1979" t="n">
+        <v>0.9000744829591183</v>
+      </c>
+      <c r="F1979" t="n">
+        <v>-0.2625348797676849</v>
+      </c>
+      <c r="G1979" t="n">
+        <v>2.591032502886295</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240529.xlsx
+++ b/tame_output/ON/bt/strategyON_20240529.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-27.9%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-51.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>443.9%</t>
+          <t>448.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-641.5%</t>
+          <t>-639.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-38.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-286.2%</t>
+          <t>-285.3%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-32.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-139.9%</t>
+          <t>-137.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-250.2%</t>
+          <t>-247.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.2%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-186.9%</t>
+          <t>-163.0%</t>
         </is>
       </c>
     </row>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.31188830135569</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386094</v>
+        <v>3.376932391386095</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998562</v>
+        <v>3.367370539998563</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082127</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.09788851868415</v>
+        <v>-10.08104604732328</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8947091850477231</v>
+        <v>-0.8879721965033762</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.333962058260685</v>
+        <v>-2.314832843609219</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.744425411783272</v>
+        <v>1.755902940574152</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.0244186870167</v>
+        <v>-10.00757621565583</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8499495508873229</v>
+        <v>-0.8432125623429756</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.260492226593236</v>
+        <v>-2.24136301194177</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.803879012277163</v>
+        <v>1.815356541068042</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.19954310440324</v>
+        <v>-10.18270063304237</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9054440970944233</v>
+        <v>-0.8987071085500764</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.43561664397978</v>
+        <v>-2.416487429328314</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.713359582592753</v>
+        <v>1.724837111383633</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.43399519841773</v>
+        <v>-10.41715272705686</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.006444099601815</v>
+        <v>-0.9997071110574685</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.43561664397978</v>
+        <v>-2.416487429328314</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.706140417691157</v>
+        <v>1.717617946482037</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.72179904295497</v>
+        <v>-10.7049565715941</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.128237828190687</v>
+        <v>-1.12150083964634</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.723420488517018</v>
+        <v>-2.704291273865552</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.526785920194838</v>
+        <v>1.538263448985718</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.7745851985553</v>
+        <v>-10.75774272719443</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.148236500592261</v>
+        <v>-1.141499512047914</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.819095975099415</v>
+        <v>-2.799966760447949</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.470496418083956</v>
+        <v>1.481973946874836</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.00661411829156</v>
+        <v>-10.98977164693069</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.238354339857651</v>
+        <v>-1.231617351313304</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.881108672287839</v>
+        <v>-2.861979457636373</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.435982528400017</v>
+        <v>1.447460057190896</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.95459860432275</v>
+        <v>-10.93775613296188</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.213557798583725</v>
+        <v>-1.206820810039378</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.881108672287839</v>
+        <v>-2.861979457636373</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.439972864086418</v>
+        <v>1.451450392877297</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.09627044604687</v>
+        <v>-11.079427974686</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.271701762172115</v>
+        <v>-1.264964773627768</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.881108672287839</v>
+        <v>-2.861979457636373</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.438497637187676</v>
+        <v>1.449975165978556</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.04667960162203</v>
+        <v>-11.02983713026116</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.236812014237309</v>
+        <v>-1.230075025692962</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.831517827863005</v>
+        <v>-2.812388613211539</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.483305554007449</v>
+        <v>1.494783082798328</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.84752749438493</v>
+        <v>-10.83068502302407</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.170202304989152</v>
+        <v>-1.163465316444805</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.666195301913191</v>
+        <v>-2.647066087261726</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.569447935930654</v>
+        <v>1.580925464721533</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.62168234166552</v>
+        <v>-10.60483987030466</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.070285170865179</v>
+        <v>-1.063548182320833</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.624268626326028</v>
+        <v>-2.605139411674562</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.60418301431916</v>
+        <v>1.61566054311004</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.49710368532793</v>
+        <v>-10.48026121396706</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.019314563774083</v>
+        <v>-1.012577575229737</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.624268626326028</v>
+        <v>-2.605139411674562</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.605322158875219</v>
+        <v>1.616799687666099</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.54999897337222</v>
+        <v>-10.53315650201135</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.037838904829691</v>
+        <v>-1.031101916285344</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.619313280237582</v>
+        <v>-2.600184065586116</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.610929140690395</v>
+        <v>1.622406669481274</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611569</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.26609024244347</v>
+        <v>-10.2492477710826</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9185417082195544</v>
+        <v>-0.9118047196752075</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.619313280237582</v>
+        <v>-2.600184065586116</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.616662844929031</v>
+        <v>1.628140373719911</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.19472384983382</v>
+        <v>-10.17788137847295</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.899732413569561</v>
+        <v>-0.8929954250252141</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.547946887627934</v>
+        <v>-2.528817672976468</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.649745418100955</v>
+        <v>1.661222946891834</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.930886982629751</v>
+        <v>-9.914044511268884</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8040811480008405</v>
+        <v>-0.7973441594564936</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.547946887627934</v>
+        <v>-2.528817672976468</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.639861936788047</v>
+        <v>1.651339465578927</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.663645181761353</v>
+        <v>-9.646802710400486</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6990189881528552</v>
+        <v>-0.6922819996085083</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.547946887627934</v>
+        <v>-2.528817672976468</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.638027376288673</v>
+        <v>1.649504905079553</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.565738143084863</v>
+        <v>-9.548895671723995</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.66015648765572</v>
+        <v>-0.6534194991113731</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.479961137767377</v>
+        <v>-2.460831923115911</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.678518511231546</v>
+        <v>1.689996040022426</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.541784602108905</v>
+        <v>-9.524942130748038</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.649906565119843</v>
+        <v>-0.6431695765754961</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.45600759679142</v>
+        <v>-2.436878382139954</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.693559141962615</v>
+        <v>1.705036670753494</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.277724663786108</v>
+        <v>-9.260882192425241</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5575429059524764</v>
+        <v>-0.5508059174081295</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.191947658468624</v>
+        <v>-2.172818443817158</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.83873478879454</v>
+        <v>1.850212317585419</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.570645040281271</v>
+        <v>-8.553802568920403</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2774980902108424</v>
+        <v>-0.2707611016664955</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.191947658468624</v>
+        <v>-2.172818443817158</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.835947755134239</v>
+        <v>1.847425283925119</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.53046074191508</v>
+        <v>-8.513618270554213</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2610807469765248</v>
+        <v>-0.2543437584321779</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.151763360102433</v>
+        <v>-2.132634145450967</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.860401958041795</v>
+        <v>1.871879486832674</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.450390946377276</v>
+        <v>-8.433548475016408</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2296860075406464</v>
+        <v>-0.2229490189962995</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.071693564564629</v>
+        <v>-2.052564349913163</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.907810656585234</v>
+        <v>1.919288185376114</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.216909724147676</v>
+        <v>-8.200067252786809</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.128369089810954</v>
+        <v>-0.1216321012666071</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.838212342335031</v>
+        <v>-1.819083127683565</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.055823818760846</v>
+        <v>2.067301347551726</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.067243333140162</v>
+        <v>-8.050400861779295</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07139474372090771</v>
+        <v>-0.0646577551765608</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.745308851092495</v>
+        <v>-1.726179636441029</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.108673703193408</v>
+        <v>2.120151231984288</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.934967859509276</v>
+        <v>-7.918125388148408</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02311706752152576</v>
+        <v>-0.01638007897717886</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.613033377461608</v>
+        <v>-1.593904162810142</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.183406474118967</v>
+        <v>2.194884002909847</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105955</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.744368184836123</v>
+        <v>-7.727525713475256</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.05593786303537174</v>
+        <v>0.06267485157971864</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.422433702788455</v>
+        <v>-1.403304488136989</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.300581339610495</v>
+        <v>2.312058868401375</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75388257196099</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.495368386152542</v>
+        <v>-7.478525914791675</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.168444123732463</v>
+        <v>0.1751811122768099</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.422433702788455</v>
+        <v>-1.403304488136989</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.313487680834154</v>
+        <v>2.324965209625034</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607647</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.600958375925646</v>
+        <v>-7.584115904564779</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.001767801775997668</v>
+        <v>0.004969186768349232</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.528023692561559</v>
+        <v>-1.508894477910093</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.122157757371073</v>
+        <v>2.133635286161953</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.619693278044243</v>
+        <v>-7.602850806683376</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.03928257925364997</v>
+        <v>0.04601956779799687</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.528023692561559</v>
+        <v>-1.508894477910093</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.170702099248159</v>
+        <v>2.182179628039039</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.471753236636644</v>
+        <v>-7.454910765275777</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.02142032687147788</v>
+        <v>-0.01468333832713098</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.507702776653002</v>
+        <v>-1.488573562001536</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.063015726105126</v>
+        <v>2.074493254896006</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.45459508650535</v>
+        <v>-7.437752615144483</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02327105307243826</v>
+        <v>-0.01653406452809136</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.471415411870242</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.064596629930425</v>
+        <v>2.076074158721304</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.411046679734659</v>
+        <v>-7.394204208373792</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.01281230245925524</v>
+        <v>-0.006075313914908342</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.471415411870242</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.057636017835332</v>
+        <v>2.069113546626211</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.168898286280801</v>
+        <v>-7.152055814919934</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09850940930343111</v>
+        <v>0.105246397847778</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.471415411870242</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.072098372216475</v>
+        <v>2.083575901007354</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.105668914512453</v>
+        <v>-7.088826443151586</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1183332784699656</v>
+        <v>0.1250702670143125</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.490544626521707</v>
+        <v>-1.471415411870242</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.06663049267567</v>
+        <v>2.078108021466549</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.982377779695322</v>
+        <v>-6.965535308334455</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1651478264073947</v>
+        <v>0.1718848149517416</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.367253491704577</v>
+        <v>-1.348124277053111</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.138103267576525</v>
+        <v>2.149580796367405</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919911</v>
+        <v>3.812453678919909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.961228580791879</v>
+        <v>-6.944386109431012</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.181308484206097</v>
+        <v>0.1880454727504439</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.346104292801134</v>
+        <v>-1.326975078149668</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.158493765155916</v>
+        <v>2.169971293946796</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318096</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.717463138808434</v>
+        <v>-6.700620667447567</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2745953693465255</v>
+        <v>0.2813323578908724</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.346104292801134</v>
+        <v>-1.326975078149668</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.154274473502967</v>
+        <v>2.165752002293846</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057528</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.570566111090564</v>
+        <v>-6.553723639729697</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3354784943536897</v>
+        <v>0.3422154828980366</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.298446050822545</v>
+        <v>-1.27931683617108</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.184993732610136</v>
+        <v>2.196471261401015</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.320715717141489</v>
+        <v>-6.303873245780622</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4281607269170218</v>
+        <v>0.4348977154613687</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.298446050822545</v>
+        <v>-1.27931683617108</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.177735807593838</v>
+        <v>2.189213336384717</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.144823624674057</v>
+        <v>-6.12798115331319</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5021166874246434</v>
+        <v>0.5088536759689903</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.298446050822545</v>
+        <v>-1.27931683617108</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.181334931114487</v>
+        <v>2.192812459905366</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.973377161651594</v>
+        <v>-5.956534690290726</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5840227786881824</v>
+        <v>0.5907597672325293</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.126999587800082</v>
+        <v>-1.107870373148617</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.297530314982518</v>
+        <v>2.309007843773398</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.748344161982771</v>
+        <v>-5.731501690621903</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6730564561720089</v>
+        <v>0.6797934447163558</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9019665881312596</v>
+        <v>-0.8828373734797937</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.431570592400109</v>
+        <v>2.443048121190988</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.684708419748836</v>
+        <v>-5.667865948387969</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7032055541198998</v>
+        <v>0.7099425426642467</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8383308458973251</v>
+        <v>-0.8192016312458592</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.474446838794787</v>
+        <v>2.485924367585667</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.591708378542938</v>
+        <v>-5.574865907182071</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7215998293860548</v>
+        <v>0.7283368179304017</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8383308458973251</v>
+        <v>-0.8192016312458592</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.455641097578583</v>
+        <v>2.467118626369462</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.79769488424229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.351277881738078</v>
+        <v>-5.33443541037721</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8195151047328761</v>
+        <v>0.826252093277223</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5979003490924648</v>
+        <v>-0.5787711344409989</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.601642472286376</v>
+        <v>2.613120001077256</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.279035313566883</v>
+        <v>-5.262192842206016</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8523414458361742</v>
+        <v>0.8590784343805211</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5979003490924648</v>
+        <v>-0.5787711344409989</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.605571786121196</v>
+        <v>2.617049314912076</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.226036991285495</v>
+        <v>-5.209194519924628</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8742193586660694</v>
+        <v>0.8809563472104163</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.542564090090526</v>
+        <v>-0.5234348754390601</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.639452125439699</v>
+        <v>2.650929654230579</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.117232105805768</v>
+        <v>-5.100389634444901</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9147393840779539</v>
+        <v>0.9214763726223008</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.542564090090526</v>
+        <v>-0.5234348754390601</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.636450196659693</v>
+        <v>2.647927725450573</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.897211307768758</v>
+        <v>-4.88036883640789</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.004326740303372</v>
+        <v>1.011063728847719</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4013442450225457</v>
+        <v>-0.3822150303710798</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.722761140711095</v>
+        <v>2.734238669501975</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.76434361870548</v>
+        <v>-4.747501147344613</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.073367998730506</v>
+        <v>1.080104987274853</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4013442450225457</v>
+        <v>-0.3822150303710798</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.738655323512919</v>
+        <v>2.750132852303798</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.60482851518611</v>
+        <v>-4.587986043825243</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.138319884578556</v>
+        <v>1.145056873122903</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2418291415031758</v>
+        <v>-0.2226999268517099</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.835510230064842</v>
+        <v>2.846987758855722</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.460156370086373</v>
+        <v>-4.443313898725505</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.206276845179891</v>
+        <v>1.213013833724238</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.09715699640343839</v>
+        <v>-0.0780277817519725</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.932401619686125</v>
+        <v>2.943879148477004</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.520031197444065</v>
+        <v>-4.503188726083198</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.16836440563824</v>
+        <v>1.175101394182587</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1570318237611305</v>
+        <v>-0.1379026091096646</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.882514214672935</v>
+        <v>2.893991743463815</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674518</v>
+        <v>3.762647477674517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.433231699665056</v>
+        <v>-4.416389228304189</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.22548469807241</v>
+        <v>1.232221686616757</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1570318237611305</v>
+        <v>-0.1379026091096646</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.904914707995502</v>
+        <v>2.916392236786381</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.435701406126862</v>
+        <v>-4.418858934765995</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.2245692168611</v>
+        <v>1.231306205405446</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1595015302229367</v>
+        <v>-0.1403723155714708</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.90350528549183</v>
+        <v>2.914982814282709</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.504071592450872</v>
+        <v>-4.487229121090005</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.208228064806197</v>
+        <v>1.214965053350544</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.1310966165352558</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.920077627388261</v>
+        <v>2.93155515617914</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.612609773367006</v>
+        <v>-4.595767302006139</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.155249501071635</v>
+        <v>1.161986489615982</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.1310966165352558</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.910514336020152</v>
+        <v>2.921991864811031</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.643602932695711</v>
+        <v>-4.626760461334844</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9675618023805399</v>
+        <v>0.9742987909248868</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.1310966165352558</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.735223901060539</v>
+        <v>2.746701429851418</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.468128672903243</v>
+        <v>-4.451286201542375</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.042318738289315</v>
+        <v>1.049055726833662</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.1310966165352558</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.739791133052327</v>
+        <v>2.751268661843206</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.579064925544492</v>
+        <v>-4.562222454183624</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9736862659940226</v>
+        <v>0.9804232545383695</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1502258311867217</v>
+        <v>-0.1310966165352558</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.715533161813534</v>
+        <v>2.727010690604413</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.782091503087725</v>
+        <v>-4.765249031726857</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8956070201966349</v>
+        <v>0.9023440087409818</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3532524087299551</v>
+        <v>-0.3341231940784892</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.596848600507499</v>
+        <v>2.608326129298379</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.760703407736505</v>
+        <v>-4.748484851655446</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9143346447692551</v>
+        <v>0.9192220672016786</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3532524087299551</v>
+        <v>-0.3341231940784892</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.607020986939632</v>
+        <v>2.618498515730511</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.674459944710128</v>
+        <v>-4.662241388629068</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9437783005536664</v>
+        <v>0.9486657229860902</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3532524087299551</v>
+        <v>-0.3341231940784892</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.601967257513492</v>
+        <v>2.613444786304371</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.719766764109107</v>
+        <v>-4.707548208028048</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9174313482386001</v>
+        <v>0.9223187706710236</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3940625717391859</v>
+        <v>-0.37493335708772</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.569256935152479</v>
+        <v>2.580734463943358</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.596639057115024</v>
+        <v>-4.584420501033965</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9672343040693347</v>
+        <v>0.9721217265017585</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3940625717391859</v>
+        <v>-0.37493335708772</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.569808808185581</v>
+        <v>2.58128633697646</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.503828575664165</v>
+        <v>-4.491610019583105</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9336311885410442</v>
+        <v>0.938518610973468</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3012520902883266</v>
+        <v>-0.2821228756368607</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.554767788947462</v>
+        <v>2.566245317738341</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560429</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.455265523443135</v>
+        <v>-4.443046967362076</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9549298853540571</v>
+        <v>0.9598173077864809</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2526890380672964</v>
+        <v>-0.2335598234158305</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.585779096204681</v>
+        <v>2.59725662499556</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472741</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.342594305206885</v>
+        <v>-4.330375749125825</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9950740811602801</v>
+        <v>0.9999615035927039</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1400178198310462</v>
+        <v>-0.1208886051795803</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.648457535658154</v>
+        <v>2.659935064449034</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.230217304024212</v>
+        <v>-4.217998747943152</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.045516177464016</v>
+        <v>1.05040359989644</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1400178198310462</v>
+        <v>-0.1208886051795803</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.653948831488821</v>
+        <v>2.665426360279701</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.428451872910943</v>
+        <v>-4.416233316829883</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9777195516778634</v>
+        <v>0.982606974110287</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3382523887177767</v>
+        <v>-0.3191231740663109</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.546505291925322</v>
+        <v>2.557982820716201</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.511453153936221</v>
+        <v>-4.499234597855162</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7828747592684051</v>
+        <v>0.7877621817008287</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3568232732449505</v>
+        <v>-0.3376940585934846</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.373718481209671</v>
+        <v>2.38519601000055</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.63852016024321</v>
+        <v>-4.62630160416215</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8521976174648154</v>
+        <v>0.8570850398972392</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3568232732449505</v>
+        <v>-0.3376940585934846</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.493868141928877</v>
+        <v>2.505345670719756</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.725118743224312</v>
+        <v>-4.712900187143253</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8320712103746972</v>
+        <v>0.836958632807121</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3568232732449505</v>
+        <v>-0.3376940585934846</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.5083811680312</v>
+        <v>2.519858696822079</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913421</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.686735080666161</v>
+        <v>-4.674516524585102</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8448441167403264</v>
+        <v>0.84973153917275</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3184396106867993</v>
+        <v>-0.2993103960353334</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.528830806908459</v>
+        <v>2.540308335699339</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.509618750630995</v>
+        <v>-4.497400194549936</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9124196775996947</v>
+        <v>0.9173071000321185</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.3184396106867993</v>
+        <v>-0.2993103960353334</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.525559835753761</v>
+        <v>2.53703736454464</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793898</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.479916626654702</v>
+        <v>-4.467698070573642</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9249839189521252</v>
+        <v>0.929871341384549</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.3229097359021127</v>
+        <v>-0.3037805212506468</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.523561152386486</v>
+        <v>2.535038681177365</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.300541205415934</v>
+        <v>-4.288322649334875</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9905210627540466</v>
+        <v>0.9954084851864704</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.166132977731394</v>
+        <v>-0.1470037630799281</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.611414182595332</v>
+        <v>2.622891711386211</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.34555541893654</v>
+        <v>-4.33333686285548</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9533228326773941</v>
+        <v>0.9582102551098179</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1964818730459986</v>
+        <v>-0.1773526583945327</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.574012300738159</v>
+        <v>2.585489829529038</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.612559929208975</v>
+        <v>-4.600341373127915</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8522125909073659</v>
+        <v>0.8571000133397897</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3908449110889472</v>
+        <v>-0.3717156964374813</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.463086040251335</v>
+        <v>2.474563569042215</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.713757710646147</v>
+        <v>-4.701539154565088</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8109374002289982</v>
+        <v>0.815824822661422</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4592537246342664</v>
+        <v>-0.4401245099828005</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.421244674020645</v>
+        <v>2.432722202811525</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815454</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.681282124475375</v>
+        <v>-4.669063568394316</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8215275962516237</v>
+        <v>0.8264150186840475</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4592537246342664</v>
+        <v>-0.4401245099828005</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.418844635574962</v>
+        <v>2.430322164365841</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378103</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.662243996768078</v>
+        <v>-4.650025440687019</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8256675665427877</v>
+        <v>0.8305549889752113</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5174373359654609</v>
+        <v>-0.498308121313995</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.38045918798449</v>
+        <v>2.39193671677537</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.693370627918696</v>
+        <v>-4.681152071837637</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9907987830212208</v>
+        <v>0.9956862054536446</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.5174373359654609</v>
+        <v>-0.498308121313995</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.55804105692317</v>
+        <v>2.56951858571405</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.745691008519488</v>
+        <v>-4.733472452438429</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9707039597670377</v>
+        <v>0.9755913821994615</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4824904759565888</v>
+        <v>-0.4633612613051229</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.579842501914627</v>
+        <v>2.591320030705507</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.890013914444407</v>
+        <v>-4.877795358363348</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9189833277939961</v>
+        <v>0.9238707502264198</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4824904759565888</v>
+        <v>-0.4633612613051229</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.585851032311553</v>
+        <v>2.597328561102433</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.742270944209404</v>
+        <v>-4.730052388128345</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.057233163680019</v>
+        <v>1.062120586112443</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3146831187217056</v>
+        <v>-0.2955539040702397</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.765688094444505</v>
+        <v>2.777165623235384</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.844285626740626</v>
+        <v>-4.832067070659567</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.019220912199011</v>
+        <v>1.024108334631435</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3146831187217056</v>
+        <v>-0.2955539040702397</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.768481715975986</v>
+        <v>2.779959244766865</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.707676282646533</v>
+        <v>-4.695457726565474</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.074526998228307</v>
+        <v>1.079414420660731</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1780737746276131</v>
+        <v>-0.1589445599761473</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.8511096708241</v>
+        <v>2.862587199614979</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.850441615469183</v>
+        <v>-4.838223059388124</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.016501341839357</v>
+        <v>1.021388764271781</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3208391074502636</v>
+        <v>-0.3017098927987977</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.76453094787062</v>
+        <v>2.776008476661499</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.788143616693061</v>
+        <v>-4.775925060612002</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.107756095146627</v>
+        <v>1.112643517579051</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3208391074502636</v>
+        <v>-0.3017098927987977</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.830866501667441</v>
+        <v>2.84234403045832</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.586353419027903</v>
+        <v>-4.574134862946844</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8970530466020881</v>
+        <v>0.9019404690345119</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1228209152811092</v>
+        <v>-0.1036917006296433</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.658258289358332</v>
+        <v>2.669735818149211</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.52646273738531</v>
+        <v>-4.51424418130425</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9912995515813008</v>
+        <v>0.9961869740137244</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.06293023363851569</v>
+        <v>-0.0438010189870498</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.764482930666063</v>
+        <v>2.775960459456942</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.624203282010284</v>
+        <v>-4.611984725929225</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9668310698473546</v>
+        <v>0.9717184922797784</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.07881951177149588</v>
+        <v>-0.05969029712002999</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.769577099902318</v>
+        <v>2.781054628693198</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.800541042133213</v>
+        <v>-4.788322486052154</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8948319466228545</v>
+        <v>0.8997193690552783</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2551572718944253</v>
+        <v>-0.2360280572429594</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.662310424653232</v>
+        <v>2.673787953444112</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.79985166997199</v>
+        <v>-4.787633113890931</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8935993135272724</v>
+        <v>0.898486735959696</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2551572718944253</v>
+        <v>-0.2360280572429594</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.660802042693161</v>
+        <v>2.67227957148404</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.806422635026583</v>
+        <v>-4.794204078945524</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8908337949408716</v>
+        <v>0.8957212173732951</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2617282369490182</v>
+        <v>-0.2425990222975523</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.656722331095841</v>
+        <v>2.668199859886721</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.798468664731811</v>
+        <v>-4.786250108650751</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8940153830587803</v>
+        <v>0.898902805491204</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2617282369490182</v>
+        <v>-0.2425990222975523</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.656722331095841</v>
+        <v>2.668199859886721</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.799275307550477</v>
+        <v>-4.775876732317665</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9000744829591183</v>
+        <v>0.9094339130522435</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.2625348797676849</v>
+        <v>-0.232225645964465</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.662620102432446</v>
+        <v>2.680805642714378</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.455524524033331</v>
+        <v>3.84489034890383</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.597968705899928</v>
+        <v>2.836823307966986</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.799275307550477</v>
+        <v>-4.775876732317665</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9000744829591183</v>
+        <v>0.9094339130522435</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2625348797676849</v>
+        <v>-0.232225645964465</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.591032502886295</v>
+        <v>2.829887104953353</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240529.xlsx
+++ b/tame_output/ON/bt/strategyON_20240529.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>-21.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.0%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.2%</t>
+          <t>126.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-665.4%</t>
+          <t>-654.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-51.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-74.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.6%</t>
+          <t>434.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-639.2%</t>
+          <t>-617.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-266.5%</t>
+          <t>-262.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.4%</t>
+          <t>-37.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-285.3%</t>
+          <t>-276.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-292.6%</t>
+          <t>-281.2%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-32.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-20.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-137.5%</t>
+          <t>-135.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-247.2%</t>
+          <t>-247.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-175.9%</t>
+          <t>-169.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-163.0%</t>
+          <t>-156.8%</t>
         </is>
       </c>
     </row>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705545</v>
+        <v>3.311607601705544</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,22 +43727,22 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045693</v>
+        <v>3.317575502045692</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.7497961784502833</v>
+        <v>0.8631049029506712</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.439479989341976</v>
+        <v>3.484803479142131</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.631764624679707</v>
+        <v>1.745073349180095</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.118976717083434</v>
+        <v>4.186961951783667</v>
       </c>
     </row>
     <row r="1835">
@@ -43750,22 +43750,22 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831154</v>
+        <v>3.320996253831153</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.5532457673970779</v>
+        <v>0.6665544918974657</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.359117660783038</v>
+        <v>3.404441150583193</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.668418790368211</v>
+        <v>1.781727514868598</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.139227052358882</v>
+        <v>4.207212287059114</v>
       </c>
     </row>
     <row r="1836">
@@ -43773,22 +43773,22 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.31188830135569</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.3997263829116132</v>
+        <v>0.5130351074120011</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.2775351796163</v>
+        <v>3.322858669416455</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.705385264837735</v>
+        <v>1.818693989338123</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.141232209668043</v>
+        <v>4.209217444368275</v>
       </c>
     </row>
     <row r="1837">
@@ -43796,22 +43796,22 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.2177198195886446</v>
+        <v>0.3310285440890325</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.205221693012986</v>
+        <v>3.250545182813142</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.705385264837735</v>
+        <v>1.818693989338123</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.141721348393917</v>
+        <v>4.20970658309415</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511404</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1694975527415611</v>
+        <v>0.282806277241949</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.19001276889582</v>
+        <v>3.235336258695975</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.657162997990651</v>
+        <v>1.770471722491039</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.116867970907334</v>
+        <v>4.184853205607566</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386095</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.06763393910823401</v>
+        <v>0.04567478539215386</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.130101256653444</v>
+        <v>3.175424746453599</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.657162997990651</v>
+        <v>1.770471722491039</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.151809055404875</v>
+        <v>4.219794290105108</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998563</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.06259634838064748</v>
+        <v>0.05071237611974039</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.130693733129816</v>
+        <v>3.176017222929971</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.712807454256969</v>
+        <v>1.826116178757356</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.183773169350004</v>
+        <v>4.251758404050237</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082127</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2252224283452861</v>
+        <v>-0.1119137038448982</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.044389682767698</v>
+        <v>3.089713172567853</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.55018137429233</v>
+        <v>1.663490098792718</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.064943902994957</v>
+        <v>4.13292913769519</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757924</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2909898183946981</v>
+        <v>-0.1776810938943102</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.019100335878403</v>
+        <v>3.064423825678558</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.55018137429233</v>
+        <v>1.663490098792718</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.065961512125428</v>
+        <v>4.133946746825661</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760742</v>
+        <v>3.293766719760741</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.4962344954519427</v>
+        <v>-0.3829257709515548</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.927630497043261</v>
+        <v>2.972953986843416</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.55018137429233</v>
+        <v>1.663490098792718</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.056589544113184</v>
+        <v>4.124574778813416</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706672</v>
+        <v>3.298730590706671</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.5780063958796944</v>
+        <v>-0.4646976713793065</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.885004462827399</v>
+        <v>2.930327952627554</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.577216947698467</v>
+        <v>1.690525672198854</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.062893614112104</v>
+        <v>4.130878848812337</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296839</v>
+        <v>3.299918119296838</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6452155037515721</v>
+        <v>-0.5319067792511842</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.86288613651235</v>
+        <v>2.908209626312505</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.577216947698467</v>
+        <v>1.690525672198854</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.067658930945806</v>
+        <v>4.135644165646038</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.852781288143184</v>
+        <v>-0.7394725636427961</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.777684618874945</v>
+        <v>2.823008108675101</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.369651163306855</v>
+        <v>1.482959887807243</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.940944256430079</v>
+        <v>4.008929491130312</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153008</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.270535311690021</v>
+        <v>-1.157226587189633</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.608509900961274</v>
+        <v>2.653833390761429</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9518971397600179</v>
+        <v>1.065205864260406</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.68821873380704</v>
+        <v>3.756203968507273</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.473824781011824</v>
+        <v>-1.360516056511436</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.527060329831475</v>
+        <v>2.57238381963163</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.9899765505255895</v>
+        <v>1.103285275025977</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.710932596865305</v>
+        <v>3.778917831565538</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.681828839364901</v>
+        <v>-1.568520114864513</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.448750851044169</v>
+        <v>2.494074340844324</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.9899765505255895</v>
+        <v>1.103285275025977</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.71582474141923</v>
+        <v>3.783809976119463</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.893241260252876</v>
+        <v>-1.779932535752488</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.359267339026967</v>
+        <v>2.404590828827122</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.7785641296376145</v>
+        <v>0.8918728541380023</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.584058745224433</v>
+        <v>3.652043979924666</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.232399637841398</v>
+        <v>-2.119090913341011</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.216688287298007</v>
+        <v>2.262011777098162</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4394057520490924</v>
+        <v>0.5527144765494802</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.373648017977769</v>
+        <v>3.441633252678002</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.440890419293083</v>
+        <v>-2.327581694792695</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.153630264456102</v>
+        <v>2.198953754256256</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.230914970597408</v>
+        <v>0.3442236950977958</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.268891838845527</v>
+        <v>3.33687707354576</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.688091604058305</v>
+        <v>-2.574782879557917</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.062848540958581</v>
+        <v>2.108172030758737</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.2510683240962204</v>
+        <v>0.3643770485966082</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.289082601353383</v>
+        <v>3.357067836053615</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.180476632082402</v>
+        <v>-3.067167907582014</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.867000921792675</v>
+        <v>1.91232441159283</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-0.1280079794274885</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.994757976582657</v>
+        <v>3.06274321128289</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.565657023012474</v>
+        <v>-3.452348298512086</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.711471304233509</v>
+        <v>1.756794794033664</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-0.1280079794274885</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.993300515395521</v>
+        <v>3.061285750095753</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.909339796239137</v>
+        <v>-3.796031071738749</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.57576731839746</v>
+        <v>1.621090808197615</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.3492227559550946</v>
+        <v>-0.2359140314547067</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.930326007633806</v>
+        <v>2.998311242334038</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.115851573126158</v>
+        <v>-4.002542848625771</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.489268666298909</v>
+        <v>1.534592156099064</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.555734532842116</v>
+        <v>-0.4424258083417282</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.802525000157851</v>
+        <v>2.870510234858083</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.371692658904851</v>
+        <v>-4.258383934404463</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.388705158687692</v>
+        <v>1.434028648487847</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.555734532842116</v>
+        <v>-0.4424258083417282</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.80429792685811</v>
+        <v>2.872283161558343</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.803498452054638</v>
+        <v>-4.690189727554251</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.202315728895181</v>
+        <v>1.247639218695336</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.692152029283383</v>
+        <v>-0.5788433047829952</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.708780316460754</v>
+        <v>2.776765551160987</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.038192446187191</v>
+        <v>-4.924883721686803</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.096722906244251</v>
+        <v>1.142046396044406</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6858157620541279</v>
+        <v>-0.57250703755374</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.700866851800398</v>
+        <v>2.768852086500631</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.373855093417643</v>
+        <v>-5.260546368917256</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9610384390080351</v>
+        <v>1.00636192880819</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6858157620541279</v>
+        <v>-0.57250703755374</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.699447443456363</v>
+        <v>2.767432678156596</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.737481338317957</v>
+        <v>-5.624172613817569</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8220755012821512</v>
+        <v>0.8673989910823066</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7840373989212537</v>
+        <v>-0.6707286744208658</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.647002021570329</v>
+        <v>2.714987256270562</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.102608720956703</v>
+        <v>-5.989299996456316</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6752790632324839</v>
+        <v>0.7206025530326392</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.080348183220266</v>
+        <v>-0.9670394587198783</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.468470065996753</v>
+        <v>2.536455300696986</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.511197498137381</v>
+        <v>-6.397888773636994</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.510605096374972</v>
+        <v>0.5559285861751264</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.375628235900557</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.222078343703105</v>
+        <v>2.290063578403338</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.787773598453214</v>
+        <v>-6.674464873952827</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3951600887200994</v>
+        <v>0.4404835785202543</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.375628235900557</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.217263776174566</v>
+        <v>2.285249010874799</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.204165472740211</v>
+        <v>-7.090856748239824</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2265973896141777</v>
+        <v>0.2719208794143326</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.375628235900557</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.215257826783443</v>
+        <v>2.283243061483676</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.520777415280859</v>
+        <v>-7.407468690780473</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1102113032665977</v>
+        <v>0.1555347930667521</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.375628235900557</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.225516517452122</v>
+        <v>2.293501752152355</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.866652237265669</v>
+        <v>-7.753343512765282</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.03203906038163096</v>
+        <v>0.01328442941852392</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.375628235900557</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.221616082597818</v>
+        <v>2.28960131729805</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.030232115450053</v>
+        <v>-7.916923390949666</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.09906609160038382</v>
+        <v>-0.05374260180022894</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.375628235900557</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.220021002652818</v>
+        <v>2.288006237353051</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.326893457260251</v>
+        <v>-8.213584732759864</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2139516523952549</v>
+        <v>-0.1686281625951001</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.444371371634435</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.182554097141699</v>
+        <v>2.250539331841932</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.531924638034567</v>
+        <v>-8.418615913534181</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2999904292393847</v>
+        <v>-0.2546669394392298</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.444371371634435</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.178527792607296</v>
+        <v>2.246513027307529</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.914926026777199</v>
+        <v>-8.801617302276812</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4532930860580211</v>
+        <v>-0.4079695962578662</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.444371371634435</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.178425691285712</v>
+        <v>2.246410925985945</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.096795817762233</v>
+        <v>-8.983487093261846</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5234694864806047</v>
+        <v>-0.4781459966804502</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.739549887119858</v>
+        <v>-1.62624116261947</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.071875332666121</v>
+        <v>2.139860567366354</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.456326140266235</v>
+        <v>-9.343017415765848</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.661931312184155</v>
+        <v>-0.6166078223840006</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.739549887119858</v>
+        <v>-1.62624116261947</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.077225635964171</v>
+        <v>2.145210870664404</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.506675203720457</v>
+        <v>-9.39336647922007</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6741549176086665</v>
+        <v>-0.6288314278085116</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.78989895057408</v>
+        <v>-1.676590226073692</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.054932217848815</v>
+        <v>2.122917452549048</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.604294481141853</v>
+        <v>-9.490985756641466</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.710160877955456</v>
+        <v>-0.6648373881553016</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.887518227995477</v>
+        <v>-1.774209503495089</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.999402402017747</v>
+        <v>2.067387636717979</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.751820569147496</v>
+        <v>-9.638511844647109</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.766277756836141</v>
+        <v>-0.7209542670359865</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.03504431600112</v>
+        <v>-1.921735591500733</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.913780305535933</v>
+        <v>1.981765540236165</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.95607874447736</v>
+        <v>-9.842770019976973</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8424678298494443</v>
+        <v>-0.7971443400492895</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.162683260615109</v>
+        <v>-2.049374536114721</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.842710135886182</v>
+        <v>1.910695370586414</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.08104604732328</v>
+        <v>-9.974989211128918</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8879721965033762</v>
+        <v>-0.8455494620256316</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.314832843609219</v>
+        <v>-2.208600104084808</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.755902940574152</v>
+        <v>1.819642584288798</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.00757621565583</v>
+        <v>-9.901519379461469</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8432125623429756</v>
+        <v>-0.8007898278652306</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.24136301194177</v>
+        <v>-2.13513027241736</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.815356541068042</v>
+        <v>1.879096184782689</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.18270063304237</v>
+        <v>-10.07664379684801</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8987071085500764</v>
+        <v>-0.8562843740723309</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.416487429328314</v>
+        <v>-2.310254689803904</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.724837111383633</v>
+        <v>1.788576755098279</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.41715272705686</v>
+        <v>-10.3110958908625</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9997071110574685</v>
+        <v>-0.957284376579723</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.416487429328314</v>
+        <v>-2.310254689803904</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.717617946482037</v>
+        <v>1.781357590196683</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.7049565715941</v>
+        <v>-10.59889973539974</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.12150083964634</v>
+        <v>-1.079078105168595</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.704291273865552</v>
+        <v>-2.598058534341142</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.538263448985718</v>
+        <v>1.602003092700364</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390588</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.75774272719443</v>
+        <v>-10.65168589100007</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.141499512047914</v>
+        <v>-1.099076777570169</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.799966760447949</v>
+        <v>-2.693734020923539</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.481973946874836</v>
+        <v>1.545713590589482</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297402</v>
+        <v>3.492101641297401</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.98977164693069</v>
+        <v>-10.88371481073633</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.231617351313304</v>
+        <v>-1.18919461683556</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.861979457636373</v>
+        <v>-2.755746718111962</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.447460057190896</v>
+        <v>1.511199700905543</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322546</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.93775613296188</v>
+        <v>-10.83169929676752</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.206820810039378</v>
+        <v>-1.164398075561633</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.861979457636373</v>
+        <v>-2.755746718111962</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.451450392877297</v>
+        <v>1.515190036591944</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.079427974686</v>
+        <v>-10.97337113849164</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.264964773627768</v>
+        <v>-1.222542039150023</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.861979457636373</v>
+        <v>-2.755746718111962</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.449975165978556</v>
+        <v>1.513714809693202</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.02983713026116</v>
+        <v>-10.9237802940668</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.230075025692962</v>
+        <v>-1.187652291215217</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.812388613211539</v>
+        <v>-2.706155873687128</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.494783082798328</v>
+        <v>1.558522726512974</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.83068502302407</v>
+        <v>-10.7246281868297</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.163465316444805</v>
+        <v>-1.12104258196706</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.647066087261726</v>
+        <v>-2.540833347737315</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.580925464721533</v>
+        <v>1.644665108436179</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.60483987030466</v>
+        <v>-10.49878303411029</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.063548182320833</v>
+        <v>-1.021125447843088</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.605139411674562</v>
+        <v>-2.498906672150151</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.61566054311004</v>
+        <v>1.679400186824686</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.48026121396706</v>
+        <v>-10.3742043777727</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.012577575229737</v>
+        <v>-0.970154840751992</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.605139411674562</v>
+        <v>-2.498906672150151</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.616799687666099</v>
+        <v>1.680539331380745</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.53315650201135</v>
+        <v>-10.42709966581699</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.031101916285344</v>
+        <v>-0.9886791818075986</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.600184065586116</v>
+        <v>-2.493951326061705</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.622406669481274</v>
+        <v>1.68614631319592</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.2492477710826</v>
+        <v>-10.14319093488824</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9118047196752075</v>
+        <v>-0.8693819851974629</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.600184065586116</v>
+        <v>-2.493951326061705</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.628140373719911</v>
+        <v>1.691880017434557</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.17788137847295</v>
+        <v>-10.07182454227859</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8929954250252141</v>
+        <v>-0.8505726905474695</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.528817672976468</v>
+        <v>-2.422584933452057</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.661222946891834</v>
+        <v>1.724962590606481</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.914044511268884</v>
+        <v>-9.807987675074521</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7973441594564936</v>
+        <v>-0.754921424978749</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.528817672976468</v>
+        <v>-2.422584933452057</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.651339465578927</v>
+        <v>1.715079109293573</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.646802710400486</v>
+        <v>-9.540745874206124</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6922819996085083</v>
+        <v>-0.6498592651307633</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.528817672976468</v>
+        <v>-2.422584933452057</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.649504905079553</v>
+        <v>1.713244548794199</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.548895671723995</v>
+        <v>-9.442838835529633</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6534194991113731</v>
+        <v>-0.6109967646336281</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.460831923115911</v>
+        <v>-2.354599183591501</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.689996040022426</v>
+        <v>1.753735683737073</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.524942130748038</v>
+        <v>-9.418885294553675</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6431695765754961</v>
+        <v>-0.6007468420977511</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.436878382139954</v>
+        <v>-2.330645642615543</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.705036670753494</v>
+        <v>1.768776314468141</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.260882192425241</v>
+        <v>-9.154825356230878</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5508059174081295</v>
+        <v>-0.5083831829303849</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.172818443817158</v>
+        <v>-2.066585704292747</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.850212317585419</v>
+        <v>1.913951961300066</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.553802568920403</v>
+        <v>-8.447745732726041</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2707611016664955</v>
+        <v>-0.2283383671887504</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.172818443817158</v>
+        <v>-2.066585704292747</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.847425283925119</v>
+        <v>1.911164927639765</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.513618270554213</v>
+        <v>-8.407561434359851</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2543437584321779</v>
+        <v>-0.2119210239544329</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.132634145450967</v>
+        <v>-2.026401405926556</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.871879486832674</v>
+        <v>1.935619130547321</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.433548475016408</v>
+        <v>-8.327491638822046</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2229490189962995</v>
+        <v>-0.1805262845185545</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.052564349913163</v>
+        <v>-1.946331610388752</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.919288185376114</v>
+        <v>1.98302782909076</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.200067252786809</v>
+        <v>-8.094010416592447</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1216321012666071</v>
+        <v>-0.07920936678886203</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.819083127683565</v>
+        <v>-1.712850388159154</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.067301347551726</v>
+        <v>2.131040991266372</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.050400861779295</v>
+        <v>-7.944344025584932</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.0646577551765608</v>
+        <v>-0.02223502069881533</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.726179636441029</v>
+        <v>-1.619946896916618</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.120151231984288</v>
+        <v>2.183890875698935</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.918125388148408</v>
+        <v>-7.812068551954045</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.01638007897717886</v>
+        <v>0.02604265550056617</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.593904162810142</v>
+        <v>-1.487671423285731</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.194884002909847</v>
+        <v>2.258623646624494</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.727525713475256</v>
+        <v>-7.621468877280893</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.06267485157971864</v>
+        <v>0.1050975860574641</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.403304488136989</v>
+        <v>-1.297071748612578</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.312058868401375</v>
+        <v>2.375798512116022</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.478525914791675</v>
+        <v>-7.372469078597311</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1751811122768099</v>
+        <v>0.2176038467545554</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.403304488136989</v>
+        <v>-1.297071748612578</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.324965209625034</v>
+        <v>2.38870485333968</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.584115904564779</v>
+        <v>-7.478059068370416</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.004969186768349232</v>
+        <v>0.0473919212460947</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.508894477910093</v>
+        <v>-1.402661738385683</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.133635286161953</v>
+        <v>2.197374929876599</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987901</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.602850806683376</v>
+        <v>-7.496793970489013</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.04601956779799687</v>
+        <v>0.08844230227574235</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.508894477910093</v>
+        <v>-1.402661738385683</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.182179628039039</v>
+        <v>2.245919271753686</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710809</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.454910765275777</v>
+        <v>-7.348853929081414</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.01468333832713098</v>
+        <v>0.02773939615061449</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.488573562001536</v>
+        <v>-1.382340822477125</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.074493254896006</v>
+        <v>2.138232898610652</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.437752615144483</v>
+        <v>-7.331695778950119</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.01653406452809136</v>
+        <v>0.02588866994965411</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.471415411870242</v>
+        <v>-1.365182672345831</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.076074158721304</v>
+        <v>2.139813802435951</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.394204208373792</v>
+        <v>-7.282057545622853</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.006075313914908342</v>
+        <v>0.03878335118546739</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.471415411870242</v>
+        <v>-1.365182672345831</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.069113546626211</v>
+        <v>2.132853190340858</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.152055814919934</v>
+        <v>-7.039909152168994</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.105246397847778</v>
+        <v>0.1501050629481537</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.471415411870242</v>
+        <v>-1.365182672345831</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.083575901007354</v>
+        <v>2.147315544722001</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.088826443151586</v>
+        <v>-6.976679780400646</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1250702670143125</v>
+        <v>0.1699289321146882</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.471415411870242</v>
+        <v>-1.365182672345831</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.078108021466549</v>
+        <v>2.141847665181196</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.965535308334455</v>
+        <v>-6.853388645583515</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1718848149517416</v>
+        <v>0.2167434800521173</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.348124277053111</v>
+        <v>-1.2418915375287</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.149580796367405</v>
+        <v>2.213320440082051</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.944386109431012</v>
+        <v>-6.832239446680072</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1880454727504439</v>
+        <v>0.2329041378508201</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.326975078149668</v>
+        <v>-1.220742338625257</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.169971293946796</v>
+        <v>2.233710937661442</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.700620667447567</v>
+        <v>-6.588474004696628</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2813323578908724</v>
+        <v>0.3261910229912481</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.326975078149668</v>
+        <v>-1.220742338625257</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.165752002293846</v>
+        <v>2.229491646008493</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.553723639729697</v>
+        <v>-6.441576976978757</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3422154828980366</v>
+        <v>0.3870741479984128</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.27931683617108</v>
+        <v>-1.173084096646669</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.196471261401015</v>
+        <v>2.260210905115662</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.303873245780622</v>
+        <v>-6.191726583029682</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4348977154613687</v>
+        <v>0.4797563805617444</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.27931683617108</v>
+        <v>-1.173084096646669</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.189213336384717</v>
+        <v>2.252952980099364</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.12798115331319</v>
+        <v>-6.01583449056225</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5088536759689903</v>
+        <v>0.5537123410693661</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.27931683617108</v>
+        <v>-1.173084096646669</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.192812459905366</v>
+        <v>2.256552103620013</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.956534690290726</v>
+        <v>-5.844388027539787</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5907597672325293</v>
+        <v>0.6356184323329055</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.107870373148617</v>
+        <v>-1.001637633624206</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.309007843773398</v>
+        <v>2.372747487488044</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.731501690621903</v>
+        <v>-5.619355027870964</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6797934447163558</v>
+        <v>0.7246521098167316</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8828373734797937</v>
+        <v>-0.7766046339553828</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.443048121190988</v>
+        <v>2.506787764905635</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.667865948387969</v>
+        <v>-5.555719285637029</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7099425426642467</v>
+        <v>0.7548012077646225</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8192016312458592</v>
+        <v>-0.7129688917214483</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.485924367585667</v>
+        <v>2.549664011300313</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.574865907182071</v>
+        <v>-5.462719244431131</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7283368179304017</v>
+        <v>0.7731954830307775</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8192016312458592</v>
+        <v>-0.7129688917214483</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.467118626369462</v>
+        <v>2.530858270084109</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.33443541037721</v>
+        <v>-5.222288747626271</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.826252093277223</v>
+        <v>0.8711107583775988</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5787711344409989</v>
+        <v>-0.472538394916588</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.613120001077256</v>
+        <v>2.676859644791902</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.262192842206016</v>
+        <v>-5.150046179455076</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8590784343805211</v>
+        <v>0.9039370994808968</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5787711344409989</v>
+        <v>-0.472538394916588</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.617049314912076</v>
+        <v>2.680788958626722</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.209194519924628</v>
+        <v>-5.097047857173688</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8809563472104163</v>
+        <v>0.925815012310792</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5234348754390601</v>
+        <v>-0.4172021359146492</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.650929654230579</v>
+        <v>2.714669297945226</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.100389634444901</v>
+        <v>-4.988242971693961</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9214763726223008</v>
+        <v>0.9663350377226765</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5234348754390601</v>
+        <v>-0.4172021359146492</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.647927725450573</v>
+        <v>2.711667369165219</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.88036883640789</v>
+        <v>-4.768222173656951</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.011063728847719</v>
+        <v>1.055922393948095</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3822150303710798</v>
+        <v>-0.2759822908466689</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.734238669501975</v>
+        <v>2.797978313216622</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.747501147344613</v>
+        <v>-4.635354484593673</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.080104987274853</v>
+        <v>1.124963652375229</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3822150303710798</v>
+        <v>-0.2759822908466689</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.750132852303798</v>
+        <v>2.813872496018445</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.587986043825243</v>
+        <v>-4.475839381074303</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.145056873122903</v>
+        <v>1.189915538223279</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2226999268517099</v>
+        <v>-0.116467187327299</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.846987758855722</v>
+        <v>2.910727402570369</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.443313898725505</v>
+        <v>-4.457131614563587</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.213013833724238</v>
+        <v>1.207486747389005</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.0780277817519725</v>
+        <v>-0.09775942081658245</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.943879148477004</v>
+        <v>2.932040165038238</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.503188726083198</v>
+        <v>-4.517006441921279</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.175101394182587</v>
+        <v>1.169574307847354</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1379026091096646</v>
+        <v>-0.1576342481742746</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.893991743463815</v>
+        <v>2.882152760025049</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674517</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.416389228304189</v>
+        <v>-4.43020694414227</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.232221686616757</v>
+        <v>1.226694600281524</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1379026091096646</v>
+        <v>-0.1576342481742746</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.916392236786381</v>
+        <v>2.904553253347615</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.418858934765995</v>
+        <v>-4.432676650604076</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.231306205405446</v>
+        <v>1.225779119070214</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1403723155714708</v>
+        <v>-0.1601039546360807</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.914982814282709</v>
+        <v>2.903143830843943</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.487229121090005</v>
+        <v>-4.501046836928086</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.214965053350544</v>
+        <v>1.209437967015312</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1310966165352558</v>
+        <v>-0.1508282555998658</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.93155515617914</v>
+        <v>2.919716172740374</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.595767302006139</v>
+        <v>-4.60958501784422</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.161986489615982</v>
+        <v>1.156459403280749</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1310966165352558</v>
+        <v>-0.1508282555998658</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.921991864811031</v>
+        <v>2.910152881372266</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.626760461334844</v>
+        <v>-4.640578177172926</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9742987909248868</v>
+        <v>0.968771704589654</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1310966165352558</v>
+        <v>-0.1508282555998658</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.746701429851418</v>
+        <v>2.734862446412652</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.451286201542375</v>
+        <v>-4.465103917380457</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.049055726833662</v>
+        <v>1.043528640498429</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1310966165352558</v>
+        <v>-0.1508282555998658</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.751268661843206</v>
+        <v>2.739429678404441</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.562222454183624</v>
+        <v>-4.576040170021706</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9804232545383695</v>
+        <v>0.974896168203137</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1310966165352558</v>
+        <v>-0.1508282555998658</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.727010690604413</v>
+        <v>2.715171707165648</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.765249031726857</v>
+        <v>-4.779066747564939</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9023440087409818</v>
+        <v>0.8968169224057492</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3341231940784892</v>
+        <v>-0.3538548331430992</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.608326129298379</v>
+        <v>2.596487145859613</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.748484851655446</v>
+        <v>-4.621141148629646</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9192220672016786</v>
+        <v>0.9701595484119987</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3341231940784892</v>
+        <v>-0.3538548331430992</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.618498515730511</v>
+        <v>2.606659532291745</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.662241388629068</v>
+        <v>-4.534897685603268</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9486657229860902</v>
+        <v>0.99960320419641</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3341231940784892</v>
+        <v>-0.3538548331430992</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.613444786304371</v>
+        <v>2.601605802865606</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.707548208028048</v>
+        <v>-4.580204505002248</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9223187706710236</v>
+        <v>0.9732562518813437</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.37493335708772</v>
+        <v>-0.39466499615233</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.580734463943358</v>
+        <v>2.568895480504592</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.584420501033965</v>
+        <v>-4.457076798008165</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9721217265017585</v>
+        <v>1.023059207712079</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.37493335708772</v>
+        <v>-0.39466499615233</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.58128633697646</v>
+        <v>2.569447353537694</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.491610019583105</v>
+        <v>-4.364266316557305</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.938518610973468</v>
+        <v>0.989456092183788</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2821228756368607</v>
+        <v>-0.3018545147014706</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.566245317738341</v>
+        <v>2.554406334299575</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.443046967362076</v>
+        <v>-4.315703264336276</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9598173077864809</v>
+        <v>1.010754788996801</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2335598234158305</v>
+        <v>-0.2532914624804404</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.59725662499556</v>
+        <v>2.585417641556794</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.330375749125825</v>
+        <v>-4.203032046100025</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9999615035927039</v>
+        <v>1.050898984803024</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1208886051795803</v>
+        <v>-0.1406202442441902</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.659935064449034</v>
+        <v>2.648096081010268</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.217998747943152</v>
+        <v>-4.090655044917352</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.05040359989644</v>
+        <v>1.10134108110676</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1208886051795803</v>
+        <v>-0.1406202442441902</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.665426360279701</v>
+        <v>2.653587376840935</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.416233316829883</v>
+        <v>-4.288889613804083</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.982606974110287</v>
+        <v>1.033544455320607</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3191231740663109</v>
+        <v>-0.3388548131309208</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.557982820716201</v>
+        <v>2.546143837277436</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.499234597855162</v>
+        <v>-4.371890894829362</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7877621817008287</v>
+        <v>0.8386996629111487</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3376940585934846</v>
+        <v>-0.3574256976580946</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.38519601000055</v>
+        <v>2.373357026561784</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.62630160416215</v>
+        <v>-4.49895790113635</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8570850398972392</v>
+        <v>0.9080225211075592</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3376940585934846</v>
+        <v>-0.3574256976580946</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.505345670719756</v>
+        <v>2.49350668728099</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.712900187143253</v>
+        <v>-4.585556484117453</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.836958632807121</v>
+        <v>0.8878961140174408</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3376940585934846</v>
+        <v>-0.3574256976580946</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.519858696822079</v>
+        <v>2.508019713383313</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913421</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.674516524585102</v>
+        <v>-4.547172821559302</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.84973153917275</v>
+        <v>0.9006690203830701</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2993103960353334</v>
+        <v>-0.3190420350999434</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.540308335699339</v>
+        <v>2.528469352260573</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.497400194549936</v>
+        <v>-4.370056491524136</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9173071000321185</v>
+        <v>0.9682445812424385</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2993103960353334</v>
+        <v>-0.3190420350999434</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.53703736454464</v>
+        <v>2.525198381105874</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793898</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.467698070573642</v>
+        <v>-4.340354367547842</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.929871341384549</v>
+        <v>0.980808822594869</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.3037805212506468</v>
+        <v>-0.3235121603152568</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.535038681177365</v>
+        <v>2.523199697738599</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011232</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.288322649334875</v>
+        <v>-4.160978946309075</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9954084851864704</v>
+        <v>1.04634596639679</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1470037630799281</v>
+        <v>-0.1667354021445381</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.622891711386211</v>
+        <v>2.611052727947445</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.33333686285548</v>
+        <v>-4.205993159829681</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9582102551098179</v>
+        <v>1.009147736320138</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1773526583945327</v>
+        <v>-0.1970842974591427</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.585489829529038</v>
+        <v>2.573650846090272</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.600341373127915</v>
+        <v>-4.472997670102116</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8571000133397897</v>
+        <v>0.9080374945501093</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3717156964374813</v>
+        <v>-0.3914473355020913</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.474563569042215</v>
+        <v>2.462724585603449</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.701539154565088</v>
+        <v>-4.574195451539289</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.815824822661422</v>
+        <v>0.8667623038717416</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4401245099828005</v>
+        <v>-0.4598561490474105</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.432722202811525</v>
+        <v>2.420883219372759</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.669063568394316</v>
+        <v>-4.541719865368517</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8264150186840475</v>
+        <v>0.8773524998943671</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4401245099828005</v>
+        <v>-0.4598561490474105</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.430322164365841</v>
+        <v>2.418483180927075</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.650025440687019</v>
+        <v>-4.52268173766122</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8305549889752113</v>
+        <v>0.8814924701855311</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.498308121313995</v>
+        <v>-0.518039760378605</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.39193671677537</v>
+        <v>2.380097733336604</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.681152071837637</v>
+        <v>-4.553808368811838</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9956862054536446</v>
+        <v>1.046623686663964</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.498308121313995</v>
+        <v>-0.518039760378605</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.56951858571405</v>
+        <v>2.557679602275284</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.733472452438429</v>
+        <v>-4.60612874941263</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9755913821994615</v>
+        <v>1.026528863409781</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4633612613051229</v>
+        <v>-0.4830929003697328</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.591320030705507</v>
+        <v>2.579481047266741</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.877795358363348</v>
+        <v>-4.750451655337549</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9238707502264198</v>
+        <v>0.9748082314367394</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4633612613051229</v>
+        <v>-0.4830929003697328</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.597328561102433</v>
+        <v>2.585489577663667</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.730052388128345</v>
+        <v>-4.602708685102546</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.062120586112443</v>
+        <v>1.113058067322762</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2955539040702397</v>
+        <v>-0.3152855431348497</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.777165623235384</v>
+        <v>2.765326639796619</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.832067070659567</v>
+        <v>-4.704723367633767</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.024108334631435</v>
+        <v>1.075045815841755</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2955539040702397</v>
+        <v>-0.3152855431348497</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.779959244766865</v>
+        <v>2.7681202613281</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.695457726565474</v>
+        <v>-4.568114023539675</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.079414420660731</v>
+        <v>1.13035190187105</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1589445599761473</v>
+        <v>-0.1786761990407572</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.862587199614979</v>
+        <v>2.850748216176214</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.838223059388124</v>
+        <v>-4.710879356362325</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.021388764271781</v>
+        <v>1.072326245482101</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3017098927987977</v>
+        <v>-0.3214415318634076</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.776008476661499</v>
+        <v>2.764169493222734</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.775925060612002</v>
+        <v>-4.648581357586203</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.112643517579051</v>
+        <v>1.16358099878937</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3017098927987977</v>
+        <v>-0.3214415318634076</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.84234403045832</v>
+        <v>2.830505047019555</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.574134862946844</v>
+        <v>-4.446791159921045</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9019404690345119</v>
+        <v>0.9528779502448315</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1036917006296433</v>
+        <v>-0.1234233396942532</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.669735818149211</v>
+        <v>2.657896834710445</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.51424418130425</v>
+        <v>-4.386900478278451</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9961869740137244</v>
+        <v>1.047124455224044</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.0438010189870498</v>
+        <v>-0.06353265805165975</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.775960459456942</v>
+        <v>2.764121476018176</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.611984725929225</v>
+        <v>-4.393917764673743</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9717184922797784</v>
+        <v>1.058945276781971</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.05969029712002999</v>
+        <v>-0.0656745758550274</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.781054628693198</v>
+        <v>2.777464061452199</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.788322486052154</v>
+        <v>-4.570255524796672</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8997193690552783</v>
+        <v>0.9869461535574708</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2360280572429594</v>
+        <v>-0.2420123359779568</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.673787953444112</v>
+        <v>2.670197386203113</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.787633113890931</v>
+        <v>-4.569566152635449</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.898486735959696</v>
+        <v>0.9857135204618888</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2360280572429594</v>
+        <v>-0.2420123359779568</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.67227957148404</v>
+        <v>2.668689004243042</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.794204078945524</v>
+        <v>-4.576137117690042</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8957212173732951</v>
+        <v>0.9829480018754879</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2425990222975523</v>
+        <v>-0.2485833010325497</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.668199859886721</v>
+        <v>2.664609292645722</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.786250108650751</v>
+        <v>-4.56818314739527</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.898902805491204</v>
+        <v>0.9861295899933968</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2425990222975523</v>
+        <v>-0.2485833010325497</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.668199859886721</v>
+        <v>2.664609292645722</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833040181947584</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.775876732317665</v>
+        <v>-4.557809771062183</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9094339130522435</v>
+        <v>0.9966606975544361</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.232225645964465</v>
+        <v>-0.2382099246994624</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.680805642714378</v>
+        <v>2.677215075473379</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.84489034890383</v>
+        <v>3.842780640277823</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.836823307966986</v>
+        <v>2.898915014526092</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.775876732317665</v>
+        <v>-4.557809771062183</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9094339130522435</v>
+        <v>0.9966606975544361</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.232225645964465</v>
+        <v>-0.2382099246994624</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.829887104953353</v>
+        <v>2.89197881151246</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240529.xlsx
+++ b/tame_output/ON/bt/strategyON_20240529.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>52.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-22.5%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-27.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.1%</t>
+          <t>126.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-654.1%</t>
+          <t>-654.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.0%</t>
+          <t>-51.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>434.5%</t>
+          <t>435.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-617.4%</t>
+          <t>-627.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-262.0%</t>
+          <t>-262.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.6%</t>
+          <t>-282.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-26.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-281.2%</t>
+          <t>-282.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.0%</t>
+          <t>-30.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-135.1%</t>
+          <t>-87.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-247.8%</t>
+          <t>-249.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-169.1%</t>
+          <t>-169.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-27.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-156.8%</t>
+          <t>-162.5%</t>
         </is>
       </c>
     </row>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705544</v>
+        <v>3.311607601705546</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,22 +43727,22 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045692</v>
+        <v>3.317575502045694</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.8631049029506712</v>
+        <v>0.8545859967075853</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.484803479142131</v>
+        <v>3.481395916644897</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.745073349180095</v>
+        <v>1.736554442937009</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.186961951783667</v>
+        <v>4.181850608037815</v>
       </c>
     </row>
     <row r="1835">
@@ -43750,22 +43750,22 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831153</v>
+        <v>3.320996253831155</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.6665544918974657</v>
+        <v>0.6580355856543798</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.404441150583193</v>
+        <v>3.401033588085959</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.781727514868598</v>
+        <v>1.773208608625513</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.207212287059114</v>
+        <v>4.202100943313262</v>
       </c>
     </row>
     <row r="1836">
@@ -43773,22 +43773,22 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.31188830135569</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.5130351074120011</v>
+        <v>0.5045162011689152</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.322858669416455</v>
+        <v>3.319451106919221</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.818693989338123</v>
+        <v>1.810175083095037</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.209217444368275</v>
+        <v>4.204106100622424</v>
       </c>
     </row>
     <row r="1837">
@@ -43796,22 +43796,22 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.3310285440890325</v>
+        <v>0.3225096378459466</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.250545182813142</v>
+        <v>3.247137620315907</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.818693989338123</v>
+        <v>1.810175083095037</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.20970658309415</v>
+        <v>4.204595239348298</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511404</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.282806277241949</v>
+        <v>0.274287370998863</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.235336258695975</v>
+        <v>3.23192869619874</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.770471722491039</v>
+        <v>1.761952816247953</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.184853205607566</v>
+        <v>4.179741861861714</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386096</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.04567478539215386</v>
+        <v>0.03715587914906793</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.175424746453599</v>
+        <v>3.172017183956364</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.770471722491039</v>
+        <v>1.761952816247953</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.219794290105108</v>
+        <v>4.214682946359257</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.367370539998563</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.05071237611974039</v>
+        <v>0.04219346987665445</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.176017222929971</v>
+        <v>3.172609660432737</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.826116178757356</v>
+        <v>1.81759727251427</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.251758404050237</v>
+        <v>4.246647060304385</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082128</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.1119137038448982</v>
+        <v>-0.1204326100879841</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.089713172567853</v>
+        <v>3.086305610070619</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.663490098792718</v>
+        <v>1.654971192549632</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.13292913769519</v>
+        <v>4.127817793949339</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757923</v>
+        <v>3.293490533757925</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.1776810938943102</v>
+        <v>-0.1862000001373962</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.064423825678558</v>
+        <v>3.061016263181324</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.663490098792718</v>
+        <v>1.654971192549632</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.133946746825661</v>
+        <v>4.128835403079809</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760741</v>
+        <v>3.293766719760743</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.3829257709515548</v>
+        <v>-0.3914446771946408</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.972953986843416</v>
+        <v>2.969546424346182</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.663490098792718</v>
+        <v>1.654971192549632</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.124574778813416</v>
+        <v>4.119463435067565</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706671</v>
+        <v>3.298730590706673</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.4646976713793065</v>
+        <v>-0.4732165776223924</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.930327952627554</v>
+        <v>2.926920390130319</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.690525672198854</v>
+        <v>1.682006765955768</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.130878848812337</v>
+        <v>4.125767505066484</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296838</v>
+        <v>3.29991811929684</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.5319067792511842</v>
+        <v>-0.5404256854942702</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.908209626312505</v>
+        <v>2.904802063815271</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.690525672198854</v>
+        <v>1.682006765955768</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.135644165646038</v>
+        <v>4.130532821900188</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201489</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7394725636427961</v>
+        <v>-0.7479914698858821</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.823008108675101</v>
+        <v>2.819600546177866</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.482959887807243</v>
+        <v>1.474440981564157</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.008929491130312</v>
+        <v>4.00381814738446</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.157226587189633</v>
+        <v>-1.165745493432719</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.653833390761429</v>
+        <v>2.650425828264194</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.065205864260406</v>
+        <v>1.05668695801732</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.756203968507273</v>
+        <v>3.751092624761422</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537427</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.360516056511436</v>
+        <v>-1.369034962754522</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.57238381963163</v>
+        <v>2.568976257134395</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.103285275025977</v>
+        <v>1.094766368782891</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.778917831565538</v>
+        <v>3.773806487819686</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.568520114864513</v>
+        <v>-1.577039021107599</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.494074340844324</v>
+        <v>2.490666778347089</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.103285275025977</v>
+        <v>1.094766368782891</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.783809976119463</v>
+        <v>3.778698632373612</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.779932535752488</v>
+        <v>-1.788451441995574</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.404590828827122</v>
+        <v>2.401183266329888</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8918728541380023</v>
+        <v>0.8833539478949164</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.652043979924666</v>
+        <v>3.646932636178815</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.119090913341011</v>
+        <v>-2.127609819584096</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.262011777098162</v>
+        <v>2.258604214600928</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5527144765494802</v>
+        <v>0.5441955703063943</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.441633252678002</v>
+        <v>3.43652190893215</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.327581694792695</v>
+        <v>-2.336100601035781</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.198953754256256</v>
+        <v>2.195546191759022</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3442236950977958</v>
+        <v>0.3357047888547099</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.33687707354576</v>
+        <v>3.331765729799908</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.574782879557917</v>
+        <v>-2.583301785801003</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.108172030758737</v>
+        <v>2.104764468261502</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3643770485966082</v>
+        <v>0.3558581423535223</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.357067836053615</v>
+        <v>3.351956492307764</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382327</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.067167907582014</v>
+        <v>-3.075686813825099</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.91232441159283</v>
+        <v>1.908916849095596</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1280079794274885</v>
+        <v>-0.1365268856705744</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.06274321128289</v>
+        <v>3.057631867537038</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.452348298512086</v>
+        <v>-3.460867204755172</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.756794794033664</v>
+        <v>1.75338723153643</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1280079794274885</v>
+        <v>-0.1365268856705744</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.061285750095753</v>
+        <v>3.056174406349902</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.796031071738749</v>
+        <v>-3.804549977981835</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.621090808197615</v>
+        <v>1.617683245700381</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2359140314547067</v>
+        <v>-0.2444329376977926</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.998311242334038</v>
+        <v>2.993199898588187</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.002542848625771</v>
+        <v>-4.011061754868856</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.534592156099064</v>
+        <v>1.53118459360183</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.4424258083417282</v>
+        <v>-0.4509447145848141</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.870510234858083</v>
+        <v>2.865398891112232</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.258383934404463</v>
+        <v>-4.266902840647549</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.434028648487847</v>
+        <v>1.430621085990613</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.4424258083417282</v>
+        <v>-0.4509447145848141</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.872283161558343</v>
+        <v>2.867171817812491</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.690189727554251</v>
+        <v>-4.698708633797336</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.247639218695336</v>
+        <v>1.244231656198102</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.5788433047829952</v>
+        <v>-0.5873622110260811</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.776765551160987</v>
+        <v>2.771654207415136</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.924883721686803</v>
+        <v>-4.933402627929889</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.142046396044406</v>
+        <v>1.138638833547172</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.57250703755374</v>
+        <v>-0.5810259437968259</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.768852086500631</v>
+        <v>2.763740742754779</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.260546368917256</v>
+        <v>-5.269065275160341</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.00636192880819</v>
+        <v>1.002954366310956</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.57250703755374</v>
+        <v>-0.5810259437968259</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.767432678156596</v>
+        <v>2.762321334410744</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.624172613817569</v>
+        <v>-5.632691520060654</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8673989910823066</v>
+        <v>0.8639914285850723</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.6707286744208658</v>
+        <v>-0.6792475806639517</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.714987256270562</v>
+        <v>2.70987591252471</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.989299996456316</v>
+        <v>-5.997818902699401</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7206025530326392</v>
+        <v>0.7171949905354049</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9670394587198783</v>
+        <v>-0.9755583649629642</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.536455300696986</v>
+        <v>2.531343956951134</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.397888773636994</v>
+        <v>-6.406407679880079</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5559285861751264</v>
+        <v>0.5525210236778926</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.375628235900557</v>
+        <v>-1.384147142143643</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.290063578403338</v>
+        <v>2.284952234657486</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.674464873952827</v>
+        <v>-6.682983780195912</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4404835785202543</v>
+        <v>0.4370760160230205</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.375628235900557</v>
+        <v>-1.384147142143643</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.285249010874799</v>
+        <v>2.280137667128947</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.090856748239824</v>
+        <v>-7.099375654482909</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2719208794143326</v>
+        <v>0.2685133169170988</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.375628235900557</v>
+        <v>-1.384147142143643</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.283243061483676</v>
+        <v>2.278131717737824</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.407468690780473</v>
+        <v>-7.415987597023557</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1555347930667521</v>
+        <v>0.1521272305695183</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.375628235900557</v>
+        <v>-1.384147142143643</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.293501752152355</v>
+        <v>2.288390408406503</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.753343512765282</v>
+        <v>-7.761862419008366</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.01328442941852392</v>
+        <v>0.009876866921290084</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.375628235900557</v>
+        <v>-1.384147142143643</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.28960131729805</v>
+        <v>2.284489973552199</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.916923390949666</v>
+        <v>-7.925442297192751</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.05374260180022894</v>
+        <v>-0.05715016429746278</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.375628235900557</v>
+        <v>-1.384147142143643</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.288006237353051</v>
+        <v>2.2828948936072</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.213584732759864</v>
+        <v>-8.222103639002949</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1686281625951001</v>
+        <v>-0.1720357250923339</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.444371371634435</v>
+        <v>-1.452890277877521</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.250539331841932</v>
+        <v>2.24542798809608</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.418615913534181</v>
+        <v>-8.427134819777265</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2546669394392298</v>
+        <v>-0.2580745019364636</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.444371371634435</v>
+        <v>-1.452890277877521</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.246513027307529</v>
+        <v>2.241401683561677</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.801617302276812</v>
+        <v>-8.810136208519896</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4079695962578662</v>
+        <v>-0.4113771587551001</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.444371371634435</v>
+        <v>-1.452890277877521</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.246410925985945</v>
+        <v>2.241299582240093</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.983487093261846</v>
+        <v>-8.992005999504931</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4781459966804502</v>
+        <v>-0.4815535591776841</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.62624116261947</v>
+        <v>-1.634760068862556</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.139860567366354</v>
+        <v>2.134749223620502</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.343017415765848</v>
+        <v>-9.351536322008933</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6166078223840006</v>
+        <v>-0.6200153848812344</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.62624116261947</v>
+        <v>-1.634760068862556</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.145210870664404</v>
+        <v>2.140099526918553</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.39336647922007</v>
+        <v>-9.401885385463155</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6288314278085116</v>
+        <v>-0.6322389903057455</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.676590226073692</v>
+        <v>-1.685109132316778</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.122917452549048</v>
+        <v>2.117806108803197</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.490985756641466</v>
+        <v>-9.499504662884551</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6648373881553016</v>
+        <v>-0.6682449506525354</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.774209503495089</v>
+        <v>-1.782728409738175</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.067387636717979</v>
+        <v>2.062276292972128</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.638511844647109</v>
+        <v>-9.647030750890194</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7209542670359865</v>
+        <v>-0.7243618295332204</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.921735591500733</v>
+        <v>-1.930254497743819</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.981765540236165</v>
+        <v>1.976654196490314</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.842770019976973</v>
+        <v>-9.851288926220057</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7971443400492895</v>
+        <v>-0.8005519025465233</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.049374536114721</v>
+        <v>-2.057893442357807</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.910695370586414</v>
+        <v>1.905584026840563</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.974989211128918</v>
+        <v>-9.993098700426845</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8455494620256316</v>
+        <v>-0.8527932577448025</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.208600104084808</v>
+        <v>-2.229172240003383</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.819642584288798</v>
+        <v>1.807299302737654</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.901519379461469</v>
+        <v>-9.919628868759396</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8007898278652306</v>
+        <v>-0.8080336235844019</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.13513027241736</v>
+        <v>-2.155702408335934</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.879096184782689</v>
+        <v>1.866752903231544</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.07664379684801</v>
+        <v>-10.09475328614594</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8562843740723309</v>
+        <v>-0.8635281697915023</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.310254689803904</v>
+        <v>-2.330826825722478</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.788576755098279</v>
+        <v>1.776233473547135</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410275</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.3110958908625</v>
+        <v>-10.32920538016043</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.957284376579723</v>
+        <v>-0.9645281722988943</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.310254689803904</v>
+        <v>-2.330826825722478</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.781357590196683</v>
+        <v>1.769014308645539</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764399</v>
+        <v>3.4806924927644</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.59889973539974</v>
+        <v>-10.61700922469767</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.079078105168595</v>
+        <v>-1.086321900887766</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.598058534341142</v>
+        <v>-2.618630670259716</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.602003092700364</v>
+        <v>1.589659811149219</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390589</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.65168589100007</v>
+        <v>-10.66979538029799</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.099076777570169</v>
+        <v>-1.10632057328934</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.693734020923539</v>
+        <v>-2.714306156842113</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.545713590589482</v>
+        <v>1.533370309038337</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297401</v>
+        <v>3.492101641297403</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.88371481073633</v>
+        <v>-10.90182430003426</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.18919461683556</v>
+        <v>-1.19643841255473</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.755746718111962</v>
+        <v>-2.776318854030536</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.511199700905543</v>
+        <v>1.498856419354398</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322547</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.83169929676752</v>
+        <v>-10.84980878606544</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.164398075561633</v>
+        <v>-1.171641871280804</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.755746718111962</v>
+        <v>-2.776318854030536</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.515190036591944</v>
+        <v>1.502846755040799</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158925</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.97337113849164</v>
+        <v>-10.99148062778956</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.222542039150023</v>
+        <v>-1.229785834869194</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.755746718111962</v>
+        <v>-2.776318854030536</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.513714809693202</v>
+        <v>1.501371528142057</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940722</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.9237802940668</v>
+        <v>-10.94188978336473</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.187652291215217</v>
+        <v>-1.194896086934388</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.706155873687128</v>
+        <v>-2.726728009605702</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.558522726512974</v>
+        <v>1.54617944496183</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.7246281868297</v>
+        <v>-10.74273767612763</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.12104258196706</v>
+        <v>-1.128286377686231</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.540833347737315</v>
+        <v>-2.561405483655889</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.644665108436179</v>
+        <v>1.632321826885035</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.49878303411029</v>
+        <v>-10.51689252340822</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.021125447843088</v>
+        <v>-1.028369243562258</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.498906672150151</v>
+        <v>-2.519478808068726</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.679400186824686</v>
+        <v>1.667056905273542</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.3742043777727</v>
+        <v>-10.39231386707063</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.970154840751992</v>
+        <v>-0.9773986364711633</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.498906672150151</v>
+        <v>-2.519478808068726</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.680539331380745</v>
+        <v>1.668196049829601</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.42709966581699</v>
+        <v>-10.44520915511491</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9886791818075986</v>
+        <v>-0.9959229775267699</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.493951326061705</v>
+        <v>-2.514523461980279</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.68614631319592</v>
+        <v>1.673803031644776</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.14319093488824</v>
+        <v>-10.16130042418617</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8693819851974629</v>
+        <v>-0.8766257809166342</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.493951326061705</v>
+        <v>-2.514523461980279</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.691880017434557</v>
+        <v>1.679536735883413</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.07182454227859</v>
+        <v>-10.08993403157652</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8505726905474695</v>
+        <v>-0.85781648626664</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.422584933452057</v>
+        <v>-2.443157069370632</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.724962590606481</v>
+        <v>1.712619309055336</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.807987675074521</v>
+        <v>-9.826097164372449</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.754921424978749</v>
+        <v>-0.7621652206979199</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.422584933452057</v>
+        <v>-2.443157069370632</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.715079109293573</v>
+        <v>1.702735827742428</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.540745874206124</v>
+        <v>-9.558855363504051</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6498592651307633</v>
+        <v>-0.6571030608499346</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.422584933452057</v>
+        <v>-2.443157069370632</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.713244548794199</v>
+        <v>1.700901267243055</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.442838835529633</v>
+        <v>-9.460948324827561</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6109967646336281</v>
+        <v>-0.618240560352799</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.354599183591501</v>
+        <v>-2.375171319510075</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.753735683737073</v>
+        <v>1.741392402185928</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.418885294553675</v>
+        <v>-9.436994783851603</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6007468420977511</v>
+        <v>-0.6079906378169224</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.330645642615543</v>
+        <v>-2.351217778534118</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.768776314468141</v>
+        <v>1.756433032916996</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.154825356230878</v>
+        <v>-9.172934845528806</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5083831829303849</v>
+        <v>-0.5156269786495558</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.066585704292747</v>
+        <v>-2.087157840211322</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.913951961300066</v>
+        <v>1.901608679748921</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.447745732726041</v>
+        <v>-8.465855222023968</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2283383671887504</v>
+        <v>-0.2355821629079218</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.066585704292747</v>
+        <v>-2.087157840211322</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.911164927639765</v>
+        <v>1.89882164608862</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.407561434359851</v>
+        <v>-8.425670923657778</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2119210239544329</v>
+        <v>-0.2191648196736042</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.026401405926556</v>
+        <v>-2.046973541845131</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.935619130547321</v>
+        <v>1.923275848996176</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.327491638822046</v>
+        <v>-8.345601128119974</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1805262845185545</v>
+        <v>-0.1877700802377253</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.946331610388752</v>
+        <v>-1.966903746307327</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.98302782909076</v>
+        <v>1.970684547539616</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.094010416592447</v>
+        <v>-8.112119905890374</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.07920936678886203</v>
+        <v>-0.08645316250803337</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.712850388159154</v>
+        <v>-1.733422524077728</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.131040991266372</v>
+        <v>2.118697709715227</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.944344025584932</v>
+        <v>-7.962453514882859</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.02223502069881533</v>
+        <v>-0.02947881641798622</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.619946896916618</v>
+        <v>-1.640519032835192</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.183890875698935</v>
+        <v>2.17154759414779</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>3.134499697705082</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.812068551954045</v>
+        <v>-7.830178041251973</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.02604265550056617</v>
+        <v>0.002072056890545682</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.487671423285731</v>
+        <v>-1.508243559204306</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.258623646624494</v>
+        <v>2.229553562182499</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105956</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>3.137314758392719</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.621468877280893</v>
+        <v>-7.63957836657882</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1050975860574641</v>
+        <v>0.08112698744744362</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.297071748612578</v>
+        <v>-1.317643884531153</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.375798512116022</v>
+        <v>2.346728427674027</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.753882571960991</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>3.150221099616378</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.372469078597311</v>
+        <v>-7.390578567895239</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2176038467545554</v>
+        <v>0.1936332481445344</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.297071748612578</v>
+        <v>-1.317643884531153</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.38870485333968</v>
+        <v>2.359634768897686</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607647</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>3.022245170017158</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.478059068370416</v>
+        <v>-7.496168557668343</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.0473919212460947</v>
+        <v>0.02342132263607377</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.402661738385683</v>
+        <v>-1.423233874304257</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.197374929876599</v>
+        <v>2.168304845434605</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>3.070789511894245</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.496793970489013</v>
+        <v>-7.51490345978694</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.08844230227574235</v>
+        <v>0.06447170366572141</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.402661738385683</v>
+        <v>-1.423233874304257</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.245919271753686</v>
+        <v>2.216849187311691</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>2.950910589206077</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.348853929081414</v>
+        <v>-7.366963418379341</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.02773939615061449</v>
+        <v>0.00376879754059356</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.382340822477125</v>
+        <v>-1.4029129583957</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.138232898610652</v>
+        <v>2.109162814168658</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>2.942196602952599</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.331695778950119</v>
+        <v>-7.349805268248047</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.02588866994965411</v>
+        <v>0.001918071339632732</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.365182672345831</v>
+        <v>-1.385754808264405</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.139813802435951</v>
+        <v>2.110743717993956</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>2.935235990857506</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.282057545622853</v>
+        <v>-7.306256861477356</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.03878335118546739</v>
+        <v>0.01237682195281575</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.365182672345831</v>
+        <v>-1.385754808264405</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.132853190340858</v>
+        <v>2.103783105898863</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>2.949698345238649</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.039909152168994</v>
+        <v>-7.064108468023498</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1501050629481537</v>
+        <v>0.1236985337155021</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.365182672345831</v>
+        <v>-1.385754808264405</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.147315544722001</v>
+        <v>2.118245460280006</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>2.944230465697844</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.976679780400646</v>
+        <v>-7.00087909625515</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1699289321146882</v>
+        <v>0.1435224028820365</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.365182672345831</v>
+        <v>-1.385754808264405</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.141847665181196</v>
+        <v>2.112777580739201</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>2.941728559708421</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.853388645583515</v>
+        <v>-6.877587961438019</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2167434800521173</v>
+        <v>0.1903369508194657</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.2418915375287</v>
+        <v>-1.262463673447275</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.213320440082051</v>
+        <v>2.184250355640057</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919909</v>
+        <v>3.812453678919911</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>2.949429537945746</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.832239446680072</v>
+        <v>-6.856438762534576</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2329041378508201</v>
+        <v>0.2064976086181685</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.220742338625257</v>
+        <v>-1.241314474543831</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.233710937661442</v>
+        <v>2.204640853219447</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318096</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>2.945210246292797</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.588474004696628</v>
+        <v>-6.612673320551131</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3261910229912481</v>
+        <v>0.2997844937585969</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.220742338625257</v>
+        <v>-1.241314474543831</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.229491646008493</v>
+        <v>2.200421561566498</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057528</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>2.947334560212813</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.441576976978757</v>
+        <v>-6.465776292833262</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3870741479984128</v>
+        <v>0.3606676187657607</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.173084096646669</v>
+        <v>-1.193656232565243</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.260210905115662</v>
+        <v>2.231140820673667</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>2.940076635196515</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.191726583029682</v>
+        <v>-6.215925898884187</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4797563805617444</v>
+        <v>0.4533498513290928</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.173084096646669</v>
+        <v>-1.193656232565243</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.252952980099364</v>
+        <v>2.223882895657369</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>2.943675758717164</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.01583449056225</v>
+        <v>-6.040033806416755</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5537123410693661</v>
+        <v>0.5273058118367144</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.173084096646669</v>
+        <v>-1.193656232565243</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.256552103620013</v>
+        <v>2.227482019178018</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>2.957003264771717</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.844388027539787</v>
+        <v>-5.868587343394291</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6356184323329055</v>
+        <v>0.6092119031002534</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.001637633624206</v>
+        <v>-1.02220976954278</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.372747487488044</v>
+        <v>2.343677403046049</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>2.956023742388014</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.619355027870964</v>
+        <v>-5.643554343725468</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7246521098167316</v>
+        <v>0.6982455805840795</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7766046339553828</v>
+        <v>-0.7971767698739575</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.506787764905635</v>
+        <v>2.47771768046364</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>2.960718543442332</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.555719285637029</v>
+        <v>-5.579918601491534</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7548012077646225</v>
+        <v>0.7283946785319708</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7129688917214483</v>
+        <v>-0.7335410276400229</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.549664011300313</v>
+        <v>2.520593926858318</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>2.941912802226127</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.462719244431131</v>
+        <v>-5.486918560285636</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7731954830307775</v>
+        <v>0.7467889537981254</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7129688917214483</v>
+        <v>-0.7335410276400229</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.530858270084109</v>
+        <v>2.501788185642114</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>2.943655878851005</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.222288747626271</v>
+        <v>-5.246488063480776</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8711107583775988</v>
+        <v>0.8447042291449471</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.472538394916588</v>
+        <v>-0.4931105308351627</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.676859644791902</v>
+        <v>2.647789560349907</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>2.947585192685825</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.150046179455076</v>
+        <v>-5.174245495309581</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9039370994808968</v>
+        <v>0.8775305702482452</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.472538394916588</v>
+        <v>-0.4931105308351627</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.680788958626722</v>
+        <v>2.651718874184728</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>2.948263776603165</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.097047857173688</v>
+        <v>-5.121247173028193</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.925815012310792</v>
+        <v>0.8994084830781404</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4172021359146492</v>
+        <v>-0.4377742718332238</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.714669297945226</v>
+        <v>2.685599213503231</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>2.945261847823158</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.988242971693961</v>
+        <v>-5.012442287548466</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9663350377226765</v>
+        <v>0.9399285084900244</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4172021359146492</v>
+        <v>-0.4377742718332238</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.711667369165219</v>
+        <v>2.682597284723224</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>2.946840884833772</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.768222173656951</v>
+        <v>-4.792421489511455</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.055922393948095</v>
+        <v>1.029515864715443</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2759822908466689</v>
+        <v>-0.2965544267652436</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.797978313216622</v>
+        <v>2.768908228774627</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>2.962735067635596</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.635354484593673</v>
+        <v>-4.659553800448178</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.124963652375229</v>
+        <v>1.098557123142577</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2759822908466689</v>
+        <v>-0.2965544267652436</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.813872496018445</v>
+        <v>2.78480241157645</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>2.963880912075898</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.475839381074303</v>
+        <v>-4.500038696928808</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.189915538223279</v>
+        <v>1.163509008990627</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.116467187327299</v>
+        <v>-0.1370393232458736</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.910727402570369</v>
+        <v>2.881657318128374</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>2.973969014637337</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.457131614563587</v>
+        <v>-4.355366551829071</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.207486747389005</v>
+        <v>1.231465969591962</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.09775942081658245</v>
+        <v>0.007632821853863769</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.932040165038238</v>
+        <v>2.978548707749656</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>2.960006506038763</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.517006441921279</v>
+        <v>-4.415241379186763</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.169574307847354</v>
+        <v>1.193553530050311</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1576342481742746</v>
+        <v>-0.05224200550382835</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.882152760025049</v>
+        <v>2.928661302736467</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.999133802252179</v>
+        <v>2.982406999361329</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.43020694414227</v>
+        <v>-4.328441881407754</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.226694600281524</v>
+        <v>1.250673822484481</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1576342481742746</v>
+        <v>-0.05224200550382835</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.904553253347615</v>
+        <v>2.951061796059033</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.999206203625592</v>
+        <v>2.982479400734741</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.432676650604076</v>
+        <v>-4.33091158786956</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.225779119070214</v>
+        <v>1.24975834127317</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1601039546360807</v>
+        <v>-0.05471171196563451</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.903143830843943</v>
+        <v>2.949652373555361</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.010213126100294</v>
+        <v>2.993486323209444</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.501046836928086</v>
+        <v>-4.39928177419357</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.209437967015312</v>
+        <v>1.233417189218268</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1508282555998658</v>
+        <v>-0.04543601292941957</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.919716172740374</v>
+        <v>2.966224715451792</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.000649834732185</v>
+        <v>2.983923031841335</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.60958501784422</v>
+        <v>-4.507819955109704</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.156459403280749</v>
+        <v>1.180438625483706</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1508282555998658</v>
+        <v>-0.04543601292941957</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.910152881372266</v>
+        <v>2.956661424083683</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.825359399772572</v>
+        <v>2.808632596881722</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.640578177172926</v>
+        <v>-4.538813114438409</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.968771704589654</v>
+        <v>0.9927509267926107</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1508282555998658</v>
+        <v>-0.04543601292941957</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.734862446412652</v>
+        <v>2.78137098912407</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.829926631764359</v>
+        <v>2.813199828873509</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.465103917380457</v>
+        <v>-4.36333885464594</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.043528640498429</v>
+        <v>1.067507862701386</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1508282555998658</v>
+        <v>-0.04543601292941957</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.739429678404441</v>
+        <v>2.785938221115858</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.805668660525567</v>
+        <v>2.788941857634716</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.576040170021706</v>
+        <v>-4.474275107287189</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.974896168203137</v>
+        <v>0.9988753904060934</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1508282555998658</v>
+        <v>-0.04543601292941957</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.715171707165648</v>
+        <v>2.761680249877065</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.808800045745472</v>
+        <v>2.792073242854622</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.779066747564939</v>
+        <v>-4.677301684830423</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8968169224057492</v>
+        <v>0.9207961446087056</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3538548331430992</v>
+        <v>-0.248462590472653</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.596487145859613</v>
+        <v>2.64299568857103</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.818972432177604</v>
+        <v>2.802245629286754</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.621141148629646</v>
+        <v>-4.51937608589513</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9701595484119987</v>
+        <v>0.9941387706149554</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3538548331430992</v>
+        <v>-0.248462590472653</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.606659532291745</v>
+        <v>2.653168075003163</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.813918702751465</v>
+        <v>2.797191899860615</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.534897685603268</v>
+        <v>-4.433132622868752</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.99960320419641</v>
+        <v>1.023582426399367</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3538548331430992</v>
+        <v>-0.248462590472653</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.601605802865606</v>
+        <v>2.648114345577023</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.80569447819599</v>
+        <v>2.78896767530514</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.580204505002248</v>
+        <v>-4.478439442267732</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9732562518813437</v>
+        <v>0.9972354740843004</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.39466499615233</v>
+        <v>-0.2892727534818837</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.568895480504592</v>
+        <v>2.61540402321601</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.75357116580319</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.806246351229092</v>
+        <v>2.789519548338242</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.457076798008165</v>
+        <v>-4.355311735273649</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.023059207712079</v>
+        <v>1.047038429915035</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.39466499615233</v>
+        <v>-0.2892727534818837</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.569447353537694</v>
+        <v>2.615955896249112</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.735519043120457</v>
+        <v>2.718792240229607</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.364266316557305</v>
+        <v>-4.262501253822789</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.989456092183788</v>
+        <v>1.013435314386745</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3018545147014706</v>
+        <v>-0.1964622720310244</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.554406334299575</v>
+        <v>2.600914877010993</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560429</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.737392519045058</v>
+        <v>2.720665716154208</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.315703264336276</v>
+        <v>-4.213938201601759</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.010754788996801</v>
+        <v>1.034734011199757</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2532914624804404</v>
+        <v>-0.1478992198099942</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.585417641556794</v>
+        <v>2.631926184268212</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472741</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.732468227556781</v>
+        <v>2.715741424665931</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.203032046100025</v>
+        <v>-4.101266983365509</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.050898984803024</v>
+        <v>1.07487820700598</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1406202442441902</v>
+        <v>-0.03522800157374401</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.648096081010268</v>
+        <v>2.694604623721685</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.737959523387449</v>
+        <v>2.721232720496598</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.090655044917352</v>
+        <v>-3.988889982182836</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.10134108110676</v>
+        <v>1.125320303309717</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1406202442441902</v>
+        <v>-0.03522800157374401</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.653587376840935</v>
+        <v>2.700095919552352</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.749456725155988</v>
+        <v>2.732729922265138</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.288889613804083</v>
+        <v>-4.187124551069567</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.033544455320607</v>
+        <v>1.057523677523564</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3388548131309208</v>
+        <v>-0.2334625704604746</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.546143837277436</v>
+        <v>2.592652379988853</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.587812445156641</v>
+        <v>2.571085642265791</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.371890894829362</v>
+        <v>-4.270125832094846</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8386996629111487</v>
+        <v>0.8626788851141054</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3574256976580946</v>
+        <v>-0.2520334549876483</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.373357026561784</v>
+        <v>2.419865569273202</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.707962105875847</v>
+        <v>2.691235302984996</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.49895790113635</v>
+        <v>-4.397192838401834</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9080225211075592</v>
+        <v>0.9320017433105157</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3574256976580946</v>
+        <v>-0.2520334549876483</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.49350668728099</v>
+        <v>2.540015229992408</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.722475131978169</v>
+        <v>2.705748329087319</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.585556484117453</v>
+        <v>-4.483791421382937</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8878961140174408</v>
+        <v>0.9118753362203975</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3574256976580946</v>
+        <v>-0.2520334549876483</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.508019713383313</v>
+        <v>2.554528256094731</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.719894573320538</v>
+        <v>2.703167770429688</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.547172821559302</v>
+        <v>-4.445407758824786</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9006690203830701</v>
+        <v>0.9246482425860267</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3190420350999434</v>
+        <v>-0.2136497924294972</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.528469352260573</v>
+        <v>2.57497789497199</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.71662360216584</v>
+        <v>2.69989679927499</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.370056491524136</v>
+        <v>-4.268291428789619</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9682445812424385</v>
+        <v>0.992223803445395</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.3190420350999434</v>
+        <v>-0.2136497924294972</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.525198381105874</v>
+        <v>2.571706923817292</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.717306993927753</v>
+        <v>2.700580191036903</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.340354367547842</v>
+        <v>-4.238589304813326</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.980808822594869</v>
+        <v>1.004788044797825</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.3235121603152568</v>
+        <v>-0.2181199176448105</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.523199697738599</v>
+        <v>2.569708240450017</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011232</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.711093969234168</v>
+        <v>2.694367166343318</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.160978946309075</v>
+        <v>-4.059213883574558</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.04634596639679</v>
+        <v>1.070325188599747</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1667354021445381</v>
+        <v>-0.06134315947409186</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.611052727947445</v>
+        <v>2.657561270658863</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.691901424565757</v>
+        <v>2.675174621674907</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.205993159829681</v>
+        <v>-4.104228097095165</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.009147736320138</v>
+        <v>1.033126958523094</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1970842974591427</v>
+        <v>-0.09169205478869646</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.573650846090272</v>
+        <v>2.62015938880169</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.697592986904703</v>
+        <v>2.680866184013853</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.472997670102116</v>
+        <v>-4.3712326073676</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9080374945501093</v>
+        <v>0.9320167167530657</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3914473355020913</v>
+        <v>-0.286055092831645</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.462724585603449</v>
+        <v>2.509233128314866</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.696796908801204</v>
+        <v>2.680070105910354</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.574195451539289</v>
+        <v>-4.472430388804773</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8667623038717416</v>
+        <v>0.8907415260746983</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4598561490474105</v>
+        <v>-0.3544639063769642</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.420883219372759</v>
+        <v>2.467391762084176</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815454</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>2.677670067464671</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.541719865368517</v>
+        <v>-4.439954802634</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8773524998943671</v>
+        <v>0.9013317220973238</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4598561490474105</v>
+        <v>-0.3544639063769642</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.418483180927075</v>
+        <v>2.464991723638493</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>2.674194786672916</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.52268173766122</v>
+        <v>-4.420916674926703</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8814924701855311</v>
+        <v>0.9054716923884876</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.518039760378605</v>
+        <v>-0.4126475177081588</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.380097733336604</v>
+        <v>2.426606276048021</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>2.851776655611597</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.553808368811838</v>
+        <v>-4.452043306077321</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.046623686663964</v>
+        <v>1.070602908866921</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.518039760378605</v>
+        <v>-0.4126475177081588</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.557679602275284</v>
+        <v>2.604188144986701</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>2.85260998459773</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.60612874941263</v>
+        <v>-4.504363686678113</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.026528863409781</v>
+        <v>1.050508085612738</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4830929003697328</v>
+        <v>-0.3777006576992866</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.579481047266741</v>
+        <v>2.625989589978158</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>2.858618514994656</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.750451655337549</v>
+        <v>-4.648686592603032</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9748082314367394</v>
+        <v>0.9987874536396961</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4830929003697328</v>
+        <v>-0.3777006576992866</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.585489577663667</v>
+        <v>2.631998120375084</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>2.937771162786678</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.602708685102546</v>
+        <v>-4.500943622368029</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.113058067322762</v>
+        <v>1.137037289525719</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3152855431348497</v>
+        <v>-0.2098933004644035</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.765326639796619</v>
+        <v>2.811835182508036</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>2.940564784318159</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.704723367633767</v>
+        <v>-4.602958304899251</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.075045815841755</v>
+        <v>1.099025038044712</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3152855431348497</v>
+        <v>-0.2098933004644035</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.7681202613281</v>
+        <v>2.814628804039517</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>2.941227132709817</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.568114023539675</v>
+        <v>-4.466348960805158</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.13035190187105</v>
+        <v>1.154331124074007</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1786761990407572</v>
+        <v>-0.07328395637031099</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.850748216176214</v>
+        <v>2.897256758887631</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>2.940307609449928</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.710879356362325</v>
+        <v>-4.609114293627808</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.072326245482101</v>
+        <v>1.096305467685057</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3214415318634076</v>
+        <v>-0.2160492891929614</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.764169493222734</v>
+        <v>2.810678035934151</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.006643163246749</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.648581357586203</v>
+        <v>-4.546816294851686</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.16358099878937</v>
+        <v>1.187560220992327</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3214415318634076</v>
+        <v>-0.2160492891929614</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.830505047019555</v>
+        <v>2.877013589730972</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.715224035636147</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.446791159921045</v>
+        <v>-4.345026097186528</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9528779502448315</v>
+        <v>0.9768571724477881</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1234233396942532</v>
+        <v>-0.01803109702380701</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.657896834710445</v>
+        <v>2.704405377421863</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.785514267958322</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.386900478278451</v>
+        <v>-4.285135415543935</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.047124455224044</v>
+        <v>1.071103677427001</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.06353265805165975</v>
+        <v>0.04185958461878647</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.764121476018176</v>
+        <v>2.810630018729594</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.800142004074365</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.393917764673743</v>
+        <v>-4.382875960168909</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.058945276781971</v>
+        <v>1.046635195693054</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.0656745758550274</v>
+        <v>0.02597030648580628</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.777464061452199</v>
+        <v>2.815724187965849</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.798677984899037</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.570255524796672</v>
+        <v>-4.559213720291838</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9869461535574708</v>
+        <v>0.9746360724685545</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2420123359779568</v>
+        <v>-0.1503674536371231</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.670197386203113</v>
+        <v>2.708457512716763</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.797169602938966</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.569566152635449</v>
+        <v>-4.558524348130615</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9857135204618888</v>
+        <v>0.9734034393729722</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2420123359779568</v>
+        <v>-0.1503674536371231</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.668689004243042</v>
+        <v>2.706949130756692</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.797032470374402</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.576137117690042</v>
+        <v>-4.565095313185208</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9829480018754879</v>
+        <v>0.9706379207865714</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2485833010325497</v>
+        <v>-0.156938418691716</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.664609292645722</v>
+        <v>2.702869419159372</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.797032470374402</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.56818314739527</v>
+        <v>-4.557141342890436</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9861295899933968</v>
+        <v>0.9738195089044803</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2485833010325497</v>
+        <v>-0.156938418691716</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.664609292645722</v>
+        <v>2.702869419159372</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947584</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.803414227402206</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.557809771062183</v>
+        <v>-4.656098762742046</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9966606975544361</v>
+        <v>0.9406182979916407</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.2382099246994624</v>
+        <v>-0.2558958385433271</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.677215075473379</v>
+        <v>2.64987672427621</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.842780640277823</v>
+        <v>3.807558196848483</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.898915014526092</v>
+        <v>2.842142479228222</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.557809771062183</v>
+        <v>-4.656098762742046</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9966606975544361</v>
+        <v>0.9406182979916407</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2382099246994624</v>
+        <v>-0.2558958385433271</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.89197881151246</v>
+        <v>2.83520627621459</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240529.xlsx
+++ b/tame_output/ON/bt/strategyON_20240529.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-43.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.4%</t>
+          <t>127.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-654.9%</t>
+          <t>-665.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-52.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>435.4%</t>
+          <t>444.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-627.2%</t>
+          <t>-648.4%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-262.4%</t>
+          <t>-266.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-39.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>-87.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-282.2%</t>
+          <t>-302.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-282.1%</t>
+          <t>-292.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-33.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-87.8%</t>
+          <t>-150.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-249.6%</t>
+          <t>-270.8%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-169.7%</t>
+          <t>-175.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-14.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-162.5%</t>
+          <t>-205.9%</t>
         </is>
       </c>
     </row>
@@ -43733,16 +43733,16 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.8545859967075853</v>
+        <v>0.7497961784502833</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.481395916644897</v>
+        <v>3.439479989341976</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.736554442937009</v>
+        <v>1.631764624679707</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.181850608037815</v>
+        <v>4.118976717083434</v>
       </c>
     </row>
     <row r="1835">
@@ -43756,16 +43756,16 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.6580355856543798</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.401033588085959</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.773208608625513</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.202100943313262</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1836">
@@ -43773,22 +43773,22 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.31188830135569</v>
+        <v>3.311888301355691</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.5045162011689152</v>
+        <v>0.3997263829116132</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.319451106919221</v>
+        <v>3.2775351796163</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.810175083095037</v>
+        <v>1.705385264837735</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.204106100622424</v>
+        <v>4.141232209668043</v>
       </c>
     </row>
     <row r="1837">
@@ -43796,22 +43796,22 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279816</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.3225096378459466</v>
+        <v>0.2177198195886446</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.247137620315907</v>
+        <v>3.205221693012986</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.810175083095037</v>
+        <v>1.705385264837735</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.204595239348298</v>
+        <v>4.141721348393917</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511407</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.274287370998863</v>
+        <v>0.1694975527415611</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.23192869619874</v>
+        <v>3.19001276889582</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.761952816247953</v>
+        <v>1.657162997990651</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.179741861861714</v>
+        <v>4.116867970907334</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386097</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.03715587914906793</v>
+        <v>-0.06763393910823401</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.172017183956364</v>
+        <v>3.130101256653444</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.761952816247953</v>
+        <v>1.657162997990651</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.214682946359257</v>
+        <v>4.151809055404875</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998563</v>
+        <v>3.367370539998565</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.04219346987665445</v>
+        <v>-0.06259634838064748</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.172609660432737</v>
+        <v>3.130693733129816</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.81759727251427</v>
+        <v>1.712807454256969</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.246647060304385</v>
+        <v>4.183773169350004</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082128</v>
+        <v>3.299560092082129</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.1204326100879841</v>
+        <v>-0.2252224283452861</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.086305610070619</v>
+        <v>3.044389682767698</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.654971192549632</v>
+        <v>1.55018137429233</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.127817793949339</v>
+        <v>4.064943902994957</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757925</v>
+        <v>3.293490533757927</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.1862000001373962</v>
+        <v>-0.2909898183946981</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.061016263181324</v>
+        <v>3.019100335878403</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.654971192549632</v>
+        <v>1.55018137429233</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.128835403079809</v>
+        <v>4.065961512125428</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760743</v>
+        <v>3.293766719760745</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.3914446771946408</v>
+        <v>-0.4962344954519427</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.969546424346182</v>
+        <v>2.927630497043261</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.654971192549632</v>
+        <v>1.55018137429233</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.119463435067565</v>
+        <v>4.056589544113184</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706673</v>
+        <v>3.298730590706675</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.4732165776223924</v>
+        <v>-0.5780063958796944</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.926920390130319</v>
+        <v>2.885004462827399</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.682006765955768</v>
+        <v>1.577216947698467</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.125767505066484</v>
+        <v>4.062893614112104</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296842</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.5404256854942702</v>
+        <v>-0.6452155037515721</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.904802063815271</v>
+        <v>2.86288613651235</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.682006765955768</v>
+        <v>1.577216947698467</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.130532821900188</v>
+        <v>4.067658930945806</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201492</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7479914698858821</v>
+        <v>-0.852781288143184</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.819600546177866</v>
+        <v>2.777684618874945</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.474440981564157</v>
+        <v>1.369651163306855</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.00381814738446</v>
+        <v>3.940944256430079</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.25879198115301</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.165745493432719</v>
+        <v>-1.270535311690021</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.650425828264194</v>
+        <v>2.608509900961274</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.05668695801732</v>
+        <v>0.9518971397600179</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.751092624761422</v>
+        <v>3.68821873380704</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.369034962754522</v>
+        <v>-1.473824781011824</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.568976257134395</v>
+        <v>2.527060329831475</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.094766368782891</v>
+        <v>0.9899765505255895</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.773806487819686</v>
+        <v>3.710932596865305</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.577039021107599</v>
+        <v>-1.681828839364901</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.490666778347089</v>
+        <v>2.448750851044169</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.094766368782891</v>
+        <v>0.9899765505255895</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.778698632373612</v>
+        <v>3.71582474141923</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.788451441995574</v>
+        <v>-1.893241260252876</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.401183266329888</v>
+        <v>2.359267339026967</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8833539478949164</v>
+        <v>0.7785641296376145</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.646932636178815</v>
+        <v>3.584058745224433</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.127609819584096</v>
+        <v>-2.232399637841398</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.258604214600928</v>
+        <v>2.216688287298007</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5441955703063943</v>
+        <v>0.4394057520490924</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.43652190893215</v>
+        <v>3.373648017977769</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.336100601035781</v>
+        <v>-2.440890419293083</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.195546191759022</v>
+        <v>2.153630264456102</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3357047888547099</v>
+        <v>0.230914970597408</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.331765729799908</v>
+        <v>3.268891838845527</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.583301785801003</v>
+        <v>-2.688091604058305</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.104764468261502</v>
+        <v>2.062848540958581</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3558581423535223</v>
+        <v>0.2510683240962204</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.351956492307764</v>
+        <v>3.289082601353383</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.075686813825099</v>
+        <v>-3.180476632082402</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.908916849095596</v>
+        <v>1.867000921792675</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1365268856705744</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.057631867537038</v>
+        <v>2.994757976582657</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.460867204755172</v>
+        <v>-3.565657023012474</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.75338723153643</v>
+        <v>1.711471304233509</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1365268856705744</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.056174406349902</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.804549977981835</v>
+        <v>-3.909339796239137</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.617683245700381</v>
+        <v>1.57576731839746</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2444329376977926</v>
+        <v>-0.3492227559550946</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.993199898588187</v>
+        <v>2.930326007633806</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.011061754868856</v>
+        <v>-4.115851573126158</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.53118459360183</v>
+        <v>1.489268666298909</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.4509447145848141</v>
+        <v>-0.555734532842116</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.865398891112232</v>
+        <v>2.802525000157851</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.266902840647549</v>
+        <v>-4.371692658904851</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.430621085990613</v>
+        <v>1.388705158687692</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.4509447145848141</v>
+        <v>-0.555734532842116</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.867171817812491</v>
+        <v>2.80429792685811</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.698708633797336</v>
+        <v>-4.803498452054638</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.244231656198102</v>
+        <v>1.202315728895181</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.5873622110260811</v>
+        <v>-0.692152029283383</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.771654207415136</v>
+        <v>2.708780316460754</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.933402627929889</v>
+        <v>-5.038192446187191</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.138638833547172</v>
+        <v>1.096722906244251</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.5810259437968259</v>
+        <v>-0.6858157620541279</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.763740742754779</v>
+        <v>2.700866851800398</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.269065275160341</v>
+        <v>-5.373855093417643</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.002954366310956</v>
+        <v>0.9610384390080351</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.5810259437968259</v>
+        <v>-0.6858157620541279</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.762321334410744</v>
+        <v>2.699447443456363</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.632691520060654</v>
+        <v>-5.737481338317957</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8639914285850723</v>
+        <v>0.8220755012821512</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.6792475806639517</v>
+        <v>-0.7840373989212537</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.70987591252471</v>
+        <v>2.647002021570329</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.997818902699401</v>
+        <v>-6.102608720956703</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7171949905354049</v>
+        <v>0.6752790632324839</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9755583649629642</v>
+        <v>-1.080348183220266</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.531343956951134</v>
+        <v>2.468470065996753</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.406407679880079</v>
+        <v>-6.511197498137381</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5525210236778926</v>
+        <v>0.510605096374972</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.384147142143643</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.284952234657486</v>
+        <v>2.222078343703105</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.682983780195912</v>
+        <v>-6.787773598453214</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4370760160230205</v>
+        <v>0.3951600887200994</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.384147142143643</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.280137667128947</v>
+        <v>2.217263776174566</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.099375654482909</v>
+        <v>-7.204165472740211</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2685133169170988</v>
+        <v>0.2265973896141777</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.384147142143643</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.278131717737824</v>
+        <v>2.215257826783443</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.415987597023557</v>
+        <v>-7.520777415280859</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1521272305695183</v>
+        <v>0.1102113032665977</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.384147142143643</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.288390408406503</v>
+        <v>2.225516517452122</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.761862419008366</v>
+        <v>-7.866652237265669</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.009876866921290084</v>
+        <v>-0.03203906038163096</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.384147142143643</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.284489973552199</v>
+        <v>2.221616082597818</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.925442297192751</v>
+        <v>-8.030232115450053</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.05715016429746278</v>
+        <v>-0.09906609160038382</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.384147142143643</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.2828948936072</v>
+        <v>2.220021002652818</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.222103639002949</v>
+        <v>-8.326893457260251</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1720357250923339</v>
+        <v>-0.2139516523952549</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.452890277877521</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.24542798809608</v>
+        <v>2.182554097141699</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.427134819777265</v>
+        <v>-8.531924638034567</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2580745019364636</v>
+        <v>-0.2999904292393847</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.452890277877521</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.241401683561677</v>
+        <v>2.178527792607296</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.810136208519896</v>
+        <v>-8.914926026777199</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4113771587551001</v>
+        <v>-0.4532930860580211</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.452890277877521</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.241299582240093</v>
+        <v>2.178425691285712</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.992005999504931</v>
+        <v>-9.096795817762233</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4815535591776841</v>
+        <v>-0.5234694864806047</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.634760068862556</v>
+        <v>-1.739549887119858</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.134749223620502</v>
+        <v>2.071875332666121</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.351536322008933</v>
+        <v>-9.456326140266235</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6200153848812344</v>
+        <v>-0.661931312184155</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.634760068862556</v>
+        <v>-1.739549887119858</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.140099526918553</v>
+        <v>2.077225635964171</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.401885385463155</v>
+        <v>-9.506675203720457</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6322389903057455</v>
+        <v>-0.6741549176086665</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.685109132316778</v>
+        <v>-1.78989895057408</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.117806108803197</v>
+        <v>2.054932217848815</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.499504662884551</v>
+        <v>-9.604294481141853</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6682449506525354</v>
+        <v>-0.710160877955456</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.782728409738175</v>
+        <v>-1.887518227995477</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.062276292972128</v>
+        <v>1.999402402017747</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.647030750890194</v>
+        <v>-9.751820569147496</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7243618295332204</v>
+        <v>-0.766277756836141</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.930254497743819</v>
+        <v>-2.03504431600112</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.976654196490314</v>
+        <v>1.913780305535933</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.851288926220057</v>
+        <v>-9.95607874447736</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8005519025465233</v>
+        <v>-0.8424678298494443</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.057893442357807</v>
+        <v>-2.162683260615109</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.905584026840563</v>
+        <v>1.842710135886182</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.993098700426845</v>
+        <v>-10.09788851868415</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8527932577448025</v>
+        <v>-0.8947091850477231</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.229172240003383</v>
+        <v>-2.333962058260685</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.807299302737654</v>
+        <v>1.744425411783272</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.919628868759396</v>
+        <v>-10.20236480037465</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8080336235844019</v>
+        <v>-0.9211279962305028</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.155702408335934</v>
+        <v>-2.438438339951186</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.866752903231544</v>
+        <v>1.697111344262393</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608603</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.09475328614594</v>
+        <v>-10.37748921776119</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8635281697915023</v>
+        <v>-0.9766225424376032</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.330826825722478</v>
+        <v>-2.61356275733773</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.776233473547135</v>
+        <v>1.606591914577983</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410275</v>
+        <v>3.485878594410276</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.32920538016043</v>
+        <v>-10.61194131177568</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9645281722988943</v>
+        <v>-1.077622544944995</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.330826825722478</v>
+        <v>-2.61356275733773</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.769014308645539</v>
+        <v>1.599372749676387</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.4806924927644</v>
+        <v>3.480692492764401</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.61700922469767</v>
+        <v>-10.89974515631292</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.086321900887766</v>
+        <v>-1.199416273533867</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.618630670259716</v>
+        <v>-2.901366601874968</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.589659811149219</v>
+        <v>1.420018252180068</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390589</v>
+        <v>3.49371601439059</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.66979538029799</v>
+        <v>-10.95253131191325</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.10632057328934</v>
+        <v>-1.219414945935442</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.714306156842113</v>
+        <v>-2.997042088457365</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.533370309038337</v>
+        <v>1.363728750069186</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297403</v>
+        <v>3.492101641297404</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.90182430003426</v>
+        <v>-11.18456023164951</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.19643841255473</v>
+        <v>-1.309532785200832</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.776318854030536</v>
+        <v>-3.059054785645789</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.498856419354398</v>
+        <v>1.329214860385247</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322547</v>
+        <v>3.573674025322548</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.84980878606544</v>
+        <v>-11.1325447176807</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.171641871280804</v>
+        <v>-1.284736243926905</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.776318854030536</v>
+        <v>-3.059054785645789</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.502846755040799</v>
+        <v>1.333205196071648</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158925</v>
+        <v>3.600038265158926</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.99148062778956</v>
+        <v>-11.27421655940482</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.229785834869194</v>
+        <v>-1.342880207515295</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.776318854030536</v>
+        <v>-3.059054785645789</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.501371528142057</v>
+        <v>1.331729969172906</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940722</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.94188978336473</v>
+        <v>-11.22462571497998</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.194896086934388</v>
+        <v>-1.307990459580489</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.726728009605702</v>
+        <v>-3.009463941220955</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.54617944496183</v>
+        <v>1.376537885992679</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.74273767612763</v>
+        <v>-11.02547360774288</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.128286377686231</v>
+        <v>-1.241380750332332</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.561405483655889</v>
+        <v>-2.844141415271142</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.632321826885035</v>
+        <v>1.462680267915884</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.51689252340822</v>
+        <v>-10.79962845502347</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.028369243562258</v>
+        <v>-1.14146361620836</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.519478808068726</v>
+        <v>-2.802214739683978</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.667056905273542</v>
+        <v>1.49741534630439</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.39231386707063</v>
+        <v>-10.67504979868588</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9773986364711633</v>
+        <v>-1.090493009117264</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.519478808068726</v>
+        <v>-2.802214739683978</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.668196049829601</v>
+        <v>1.498554490860449</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.44520915511491</v>
+        <v>-10.72794508673017</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9959229775267699</v>
+        <v>-1.109017350172871</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.514523461980279</v>
+        <v>-2.797259393595532</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.673803031644776</v>
+        <v>1.504161472675625</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.16130042418617</v>
+        <v>-10.44403635580142</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8766257809166342</v>
+        <v>-0.9897201535627351</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.514523461980279</v>
+        <v>-2.797259393595532</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.679536735883413</v>
+        <v>1.509895176914261</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.08993403157652</v>
+        <v>-10.37266996319177</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.85781648626664</v>
+        <v>-0.9709108589127418</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.443157069370632</v>
+        <v>-2.725893000985884</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.712619309055336</v>
+        <v>1.542977750086185</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.826097164372449</v>
+        <v>-10.1088330959877</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7621652206979199</v>
+        <v>-0.8752595933440213</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.443157069370632</v>
+        <v>-2.725893000985884</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.702735827742428</v>
+        <v>1.533094268773277</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.558855363504051</v>
+        <v>-9.841591295119304</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6571030608499346</v>
+        <v>-0.7701974334960355</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.443157069370632</v>
+        <v>-2.725893000985884</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.700901267243055</v>
+        <v>1.531259708273903</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.460948324827561</v>
+        <v>-9.743684256442814</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.618240560352799</v>
+        <v>-0.7313349329989003</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.375171319510075</v>
+        <v>-2.657907251125327</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.741392402185928</v>
+        <v>1.571750843216776</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.436994783851603</v>
+        <v>-9.719730715466856</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6079906378169224</v>
+        <v>-0.7210850104630233</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.351217778534118</v>
+        <v>-2.63395371014937</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.756433032916996</v>
+        <v>1.586791473947845</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.172934845528806</v>
+        <v>-9.455670777144059</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5156269786495558</v>
+        <v>-0.6287213512956571</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.087157840211322</v>
+        <v>-2.369893771826574</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.901608679748921</v>
+        <v>1.73196712077977</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.465855222023968</v>
+        <v>-8.748591153639222</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2355821629079218</v>
+        <v>-0.3486765355540227</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.087157840211322</v>
+        <v>-2.369893771826574</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.89882164608862</v>
+        <v>1.729180087119469</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.425670923657778</v>
+        <v>-8.708406855273031</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2191648196736042</v>
+        <v>-0.3322591923197051</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.046973541845131</v>
+        <v>-2.329709473460383</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.923275848996176</v>
+        <v>1.753634290027025</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.345601128119974</v>
+        <v>-8.628337059735227</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1877700802377253</v>
+        <v>-0.3008644528838267</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.966903746307327</v>
+        <v>-2.249639677922579</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.970684547539616</v>
+        <v>1.801042988570464</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.112119905890374</v>
+        <v>-8.394855837505627</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.08645316250803337</v>
+        <v>-0.1995475351541343</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.733422524077728</v>
+        <v>-2.016158455692981</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.118697709715227</v>
+        <v>1.949056150746076</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785789</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.962453514882859</v>
+        <v>-8.245189446498113</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.02947881641798622</v>
+        <v>-0.142573189064088</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.640519032835192</v>
+        <v>-1.923254964450445</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.17154759414779</v>
+        <v>2.001906035178638</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.134499697705082</v>
+        <v>3.135382208123158</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.830178041251973</v>
+        <v>-8.209951890223268</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.002072056890545682</v>
+        <v>-0.1489549722798964</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.508243559204306</v>
+        <v>-1.888017408175599</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.229553562182499</v>
+        <v>2.002571763217799</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105956</v>
+        <v>3.784718794105955</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.137314758392719</v>
+        <v>3.138197268810795</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.63957836657882</v>
+        <v>-8.019352215550114</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.08112698744744362</v>
+        <v>-0.06990004172299802</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.317643884531153</v>
+        <v>-1.697417733502446</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.346728427674027</v>
+        <v>2.119746628709327</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960991</v>
+        <v>3.75388257196099</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.150221099616378</v>
+        <v>3.151103610034454</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.390578567895239</v>
+        <v>-7.770352416866533</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1936332481445344</v>
+        <v>0.04260621897409278</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.317643884531153</v>
+        <v>-1.697417733502446</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.359634768897686</v>
+        <v>2.132652969932987</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607647</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.022245170017158</v>
+        <v>3.023127680435235</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.496168557668343</v>
+        <v>-7.875942406639638</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.02342132263607377</v>
+        <v>-0.1276057065343674</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.423233874304257</v>
+        <v>-1.80300772327555</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.168304845434605</v>
+        <v>1.941323046469905</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.070789511894245</v>
+        <v>3.071672022312321</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.51490345978694</v>
+        <v>-7.894677308758235</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.06447170366572141</v>
+        <v>-0.08655532550471978</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.423233874304257</v>
+        <v>-1.80300772327555</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.216849187311691</v>
+        <v>1.989867388346991</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.950910589206077</v>
+        <v>2.951793099624154</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.366963418379341</v>
+        <v>-7.746737267350635</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.00376879754059356</v>
+        <v>-0.1472582316298476</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.4029129583957</v>
+        <v>-1.782686807366993</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.109162814168658</v>
+        <v>1.882181015203958</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.942196602952599</v>
+        <v>2.943079113370676</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.349805268248047</v>
+        <v>-7.729579117219341</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.001918071339632732</v>
+        <v>-0.1491089578308085</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.385754808264405</v>
+        <v>-1.765528657235699</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.110743717993956</v>
+        <v>1.883761919029257</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.935235990857506</v>
+        <v>2.936118501275582</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.306256861477356</v>
+        <v>-7.686030710448651</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.01237682195281575</v>
+        <v>-0.1386502072176254</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.385754808264405</v>
+        <v>-1.765528657235699</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.103783105898863</v>
+        <v>1.876801306934164</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.949698345238649</v>
+        <v>2.950580855656725</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.064108468023498</v>
+        <v>-7.443882316994793</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1236985337155021</v>
+        <v>-0.02732849545493909</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.385754808264405</v>
+        <v>-1.765528657235699</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.118245460280006</v>
+        <v>1.891263661315307</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.944230465697844</v>
+        <v>2.94511297611592</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.00087909625515</v>
+        <v>-7.380652945226444</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1435224028820365</v>
+        <v>-0.007504626288404648</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.385754808264405</v>
+        <v>-1.765528657235699</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.112777580739201</v>
+        <v>1.885795781774502</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.941728559708421</v>
+        <v>2.942611070126497</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.877587961438019</v>
+        <v>-7.257361810409313</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1903369508194657</v>
+        <v>0.03930992164902447</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.262463673447275</v>
+        <v>-1.642237522418568</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.184250355640057</v>
+        <v>1.957268556675357</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919911</v>
+        <v>3.812453678919912</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.949429537945746</v>
+        <v>2.950312048363823</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.856438762534576</v>
+        <v>-7.23621261150587</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2064976086181685</v>
+        <v>0.05547057944772726</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.241314474543831</v>
+        <v>-1.621088323515125</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.204640853219447</v>
+        <v>1.977659054254748</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318096</v>
+        <v>3.748328408318097</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.945210246292797</v>
+        <v>2.946092756710873</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.612673320551131</v>
+        <v>-6.992447169522426</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2997844937585969</v>
+        <v>0.1487574645881558</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.241314474543831</v>
+        <v>-1.621088323515125</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.200421561566498</v>
+        <v>1.973439762601799</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057528</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.947334560212813</v>
+        <v>2.948217070630889</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.465776292833262</v>
+        <v>-6.845550141804555</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3606676187657607</v>
+        <v>0.2096405895953199</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.193656232565243</v>
+        <v>-1.573430081536537</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.231140820673667</v>
+        <v>2.004159021708968</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.940076635196515</v>
+        <v>2.940959145614591</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.215925898884187</v>
+        <v>-6.59569974785548</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4533498513290928</v>
+        <v>0.302322822158652</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.193656232565243</v>
+        <v>-1.573430081536537</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.223882895657369</v>
+        <v>1.99690109669267</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.943675758717164</v>
+        <v>2.94455826913524</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.040033806416755</v>
+        <v>-6.419807655388048</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5273058118367144</v>
+        <v>0.3762787826662732</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.193656232565243</v>
+        <v>-1.573430081536537</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.227482019178018</v>
+        <v>2.000500220213318</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.957003264771717</v>
+        <v>2.957885775189794</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.868587343394291</v>
+        <v>-6.248361192365585</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6092119031002534</v>
+        <v>0.4581848739298127</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.02220976954278</v>
+        <v>-1.401983618514074</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.343677403046049</v>
+        <v>2.11669560408135</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.956023742388014</v>
+        <v>2.956906252806091</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.643554343725468</v>
+        <v>-6.023328192696762</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6982455805840795</v>
+        <v>0.5472185514136387</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7971767698739575</v>
+        <v>-1.176950618845251</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.47771768046364</v>
+        <v>2.250735881498941</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.960718543442332</v>
+        <v>2.961601053860408</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.579918601491534</v>
+        <v>-5.959692450462827</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7283946785319708</v>
+        <v>0.5773676493615296</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7335410276400229</v>
+        <v>-1.113314876611316</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.520593926858318</v>
+        <v>2.293612127893619</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.941912802226127</v>
+        <v>2.942795312644204</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.486918560285636</v>
+        <v>-5.866692409256929</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7467889537981254</v>
+        <v>0.5957619246276846</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7335410276400229</v>
+        <v>-1.113314876611316</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.501788185642114</v>
+        <v>2.274806386677414</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.943655878851005</v>
+        <v>2.944538389269081</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.246488063480776</v>
+        <v>-5.626261912452069</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8447042291449471</v>
+        <v>0.6936771999745064</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4931105308351627</v>
+        <v>-0.8728843798064561</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.647789560349907</v>
+        <v>2.420807761385208</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.947585192685825</v>
+        <v>2.948467703103901</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.174245495309581</v>
+        <v>-5.554019344280874</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8775305702482452</v>
+        <v>0.7265035410778045</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4931105308351627</v>
+        <v>-0.8728843798064561</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.651718874184728</v>
+        <v>2.424737075220028</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.948263776603165</v>
+        <v>2.949146287021241</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.121247173028193</v>
+        <v>-5.501021021999486</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8994084830781404</v>
+        <v>0.7483814539076996</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4377742718332238</v>
+        <v>-0.8175481208045172</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.685599213503231</v>
+        <v>2.458617414538531</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.945261847823158</v>
+        <v>2.946144358241235</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.012442287548466</v>
+        <v>-5.392216136519759</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9399285084900244</v>
+        <v>0.7889014793195837</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4377742718332238</v>
+        <v>-0.8175481208045172</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.682597284723224</v>
+        <v>2.455615485758525</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.946840884833772</v>
+        <v>2.947723395251849</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.792421489511455</v>
+        <v>-5.172195338482749</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.029515864715443</v>
+        <v>0.878488835545002</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2965544267652436</v>
+        <v>-0.676328275736537</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.768908228774627</v>
+        <v>2.541926429809927</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.962735067635596</v>
+        <v>2.963617578053672</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.659553800448178</v>
+        <v>-5.039327649419471</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.098557123142577</v>
+        <v>0.9475300939721363</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2965544267652436</v>
+        <v>-0.676328275736537</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.78480241157645</v>
+        <v>2.55782061261175</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.963880912075898</v>
+        <v>2.964763422493974</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.500038696928808</v>
+        <v>-4.879812545900101</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.163509008990627</v>
+        <v>1.012481979820186</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1370393232458736</v>
+        <v>-0.516813172217167</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.881657318128374</v>
+        <v>2.654675519163674</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.973969014637337</v>
+        <v>2.974851525055414</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.355366551829071</v>
+        <v>-4.735140400800364</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.231465969591962</v>
+        <v>1.080438940421521</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.007632821853863769</v>
+        <v>-0.3721410271174296</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.978548707749656</v>
+        <v>2.751566908784957</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942105</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.960006506038763</v>
+        <v>2.96088901645684</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.415241379186763</v>
+        <v>-4.795015228158056</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.193553530050311</v>
+        <v>1.04252650087987</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.05224200550382835</v>
+        <v>-0.4320158544751218</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.928661302736467</v>
+        <v>2.701679503771767</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.982406999361329</v>
+        <v>2.983289509779406</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.328441881407754</v>
+        <v>-4.708215730379047</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.250673822484481</v>
+        <v>1.09964679331404</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.05224200550382835</v>
+        <v>-0.4320158544751218</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.951061796059033</v>
+        <v>2.724079997094333</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.982479400734741</v>
+        <v>2.983361911152818</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.33091158786956</v>
+        <v>-4.710685436840853</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.24975834127317</v>
+        <v>1.09873131210273</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.05471171196563451</v>
+        <v>-0.4344855609369279</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.949652373555361</v>
+        <v>2.722670574590662</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.993486323209444</v>
+        <v>2.99436883362752</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.39928177419357</v>
+        <v>-4.779055623164863</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.233417189218268</v>
+        <v>1.082390160047827</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.04543601292941957</v>
+        <v>-0.425209861900713</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.966224715451792</v>
+        <v>2.739242916487092</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.983923031841335</v>
+        <v>2.984805542259411</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.507819955109704</v>
+        <v>-4.887593804080997</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.180438625483706</v>
+        <v>1.029411596313265</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.04543601292941957</v>
+        <v>-0.425209861900713</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.956661424083683</v>
+        <v>2.729679625118984</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.808632596881722</v>
+        <v>2.809515107299798</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.538813114438409</v>
+        <v>-4.918586963409703</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9927509267926107</v>
+        <v>0.8417238976221699</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.04543601292941957</v>
+        <v>-0.425209861900713</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.78137098912407</v>
+        <v>2.55438919015937</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.813199828873509</v>
+        <v>2.814082339291586</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.36333885464594</v>
+        <v>-4.743112703617234</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.067507862701386</v>
+        <v>0.9164808335309451</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.04543601292941957</v>
+        <v>-0.425209861900713</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.785938221115858</v>
+        <v>2.558956422151158</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.788941857634716</v>
+        <v>2.789824368052793</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.474275107287189</v>
+        <v>-4.854048956258483</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9988753904060934</v>
+        <v>0.8478483612356527</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.04543601292941957</v>
+        <v>-0.425209861900713</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.761680249877065</v>
+        <v>2.534698450912365</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.792073242854622</v>
+        <v>2.792955753272699</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.677301684830423</v>
+        <v>-5.057075533801716</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9207961446087056</v>
+        <v>0.7697691154382649</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.248462590472653</v>
+        <v>-0.6282364394439464</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.64299568857103</v>
+        <v>2.416013889606331</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.802245629286754</v>
+        <v>2.803128139704831</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.51937608589513</v>
+        <v>-4.899149934866423</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9941387706149554</v>
+        <v>0.8431117414445144</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.248462590472653</v>
+        <v>-0.6282364394439464</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.653168075003163</v>
+        <v>2.426186276038463</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.797191899860615</v>
+        <v>2.798074410278691</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.433132622868752</v>
+        <v>-4.812906471840045</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.023582426399367</v>
+        <v>0.8725553972289259</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.248462590472653</v>
+        <v>-0.6282364394439464</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.648114345577023</v>
+        <v>2.421132546612323</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.78896767530514</v>
+        <v>2.789850185723217</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.478439442267732</v>
+        <v>-4.858213291239025</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9972354740843004</v>
+        <v>0.8462084449138594</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2892727534818837</v>
+        <v>-0.6690466024531772</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.61540402321601</v>
+        <v>2.388422224251311</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.789519548338242</v>
+        <v>2.790402058756318</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.355311735273649</v>
+        <v>-4.735085584244942</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.047038429915035</v>
+        <v>0.8960114007445943</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2892727534818837</v>
+        <v>-0.6690466024531772</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.615955896249112</v>
+        <v>2.388974097284412</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.718792240229607</v>
+        <v>2.719674750647684</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.262501253822789</v>
+        <v>-4.642275102794082</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.013435314386745</v>
+        <v>0.8624082852163037</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1964622720310244</v>
+        <v>-0.5762361210023178</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.600914877010993</v>
+        <v>2.373933078046293</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560429</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.720665716154208</v>
+        <v>2.721548226572285</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.213938201601759</v>
+        <v>-4.593712050573052</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.034734011199757</v>
+        <v>0.8837069820293166</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1478992198099942</v>
+        <v>-0.5276730687812876</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.631926184268212</v>
+        <v>2.404944385303513</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472741</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.715741424665931</v>
+        <v>2.716623935084008</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.101266983365509</v>
+        <v>-4.481040832336802</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.07487820700598</v>
+        <v>0.9238511778355396</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.03522800157374401</v>
+        <v>-0.4150018505450374</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.694604623721685</v>
+        <v>2.467622824756986</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.721232720496598</v>
+        <v>2.722115230914675</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.988889982182836</v>
+        <v>-4.368663831154129</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.125320303309717</v>
+        <v>0.974293274139276</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.03522800157374401</v>
+        <v>-0.4150018505450374</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.700095919552352</v>
+        <v>2.473114120587653</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498864</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.732729922265138</v>
+        <v>2.733612432683214</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.187124551069567</v>
+        <v>-4.56689840004086</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.057523677523564</v>
+        <v>0.9064966483531227</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2334625704604746</v>
+        <v>-0.613236419431768</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.592652379988853</v>
+        <v>2.365670581024153</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.571085642265791</v>
+        <v>2.571968152683867</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.270125832094846</v>
+        <v>-4.649899681066139</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8626788851141054</v>
+        <v>0.7116518559436644</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2520334549876483</v>
+        <v>-0.6318073039589418</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.419865569273202</v>
+        <v>2.192883770308502</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.691235302984996</v>
+        <v>2.692117813403073</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.397192838401834</v>
+        <v>-4.776966687373127</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9320017433105157</v>
+        <v>0.7809747141400749</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2520334549876483</v>
+        <v>-0.6318073039589418</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.540015229992408</v>
+        <v>2.313033431027708</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.705748329087319</v>
+        <v>2.706630839505396</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.483791421382937</v>
+        <v>-4.86356527035423</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9118753362203975</v>
+        <v>0.7608483070499568</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2520334549876483</v>
+        <v>-0.6318073039589418</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.554528256094731</v>
+        <v>2.327546457130031</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913421</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.703167770429688</v>
+        <v>2.704050280847765</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.445407758824786</v>
+        <v>-4.825181607796079</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9246482425860267</v>
+        <v>0.7736212134155858</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2136497924294972</v>
+        <v>-0.5934236414007906</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.57497789497199</v>
+        <v>2.347996096007291</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.69989679927499</v>
+        <v>2.700779309693067</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.268291428789619</v>
+        <v>-4.648065277760913</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.992223803445395</v>
+        <v>0.8411967742749542</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2136497924294972</v>
+        <v>-0.5934236414007906</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.571706923817292</v>
+        <v>2.344725124852593</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793898</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.700580191036903</v>
+        <v>2.70146270145498</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.238589304813326</v>
+        <v>-4.618363153784619</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.004788044797825</v>
+        <v>0.8537610156273847</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2181199176448105</v>
+        <v>-0.5978937666161039</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.569708240450017</v>
+        <v>2.342726441485318</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.694367166343318</v>
+        <v>2.695249676761394</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.059213883574558</v>
+        <v>-4.438987732545852</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.070325188599747</v>
+        <v>0.9192981594293061</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.06134315947409186</v>
+        <v>-0.4411170084453853</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.657561270658863</v>
+        <v>2.430579471694163</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.675174621674907</v>
+        <v>2.676057132092984</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.104228097095165</v>
+        <v>-4.484001946066458</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.033126958523094</v>
+        <v>0.8820999293526532</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.09169205478869646</v>
+        <v>-0.4714659037599899</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.62015938880169</v>
+        <v>2.39317758983699</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.680866184013853</v>
+        <v>2.68174869443193</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.3712326073676</v>
+        <v>-4.751006456338893</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9320167167530657</v>
+        <v>0.780989687582625</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.286055092831645</v>
+        <v>-0.6658289418029384</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.509233128314866</v>
+        <v>2.282251329350167</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.680070105910354</v>
+        <v>2.680952616328431</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.472430388804773</v>
+        <v>-4.852204237776066</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8907415260746983</v>
+        <v>0.7397144969042573</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3544639063769642</v>
+        <v>-0.7342377553482575</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.467391762084176</v>
+        <v>2.240409963119477</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.677670067464671</v>
+        <v>2.678552577882748</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.439954802634</v>
+        <v>-4.819728651605294</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9013317220973238</v>
+        <v>0.7503046929268828</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3544639063769642</v>
+        <v>-0.7342377553482575</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.464991723638493</v>
+        <v>2.238009924673793</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.674194786672916</v>
+        <v>2.675077297090993</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.420916674926703</v>
+        <v>-4.800690523897996</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9054716923884876</v>
+        <v>0.7544446632180468</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4126475177081588</v>
+        <v>-0.7924213666794521</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.426606276048021</v>
+        <v>2.199624477083322</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.851776655611597</v>
+        <v>2.852659166029673</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.452043306077321</v>
+        <v>-4.831817155048615</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.070602908866921</v>
+        <v>0.9195758796964799</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4126475177081588</v>
+        <v>-0.7924213666794521</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.604188144986701</v>
+        <v>2.377206346022002</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.85260998459773</v>
+        <v>2.853492495015807</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.504363686678113</v>
+        <v>-4.884137535649407</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.050508085612738</v>
+        <v>0.8994810564422968</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3777006576992866</v>
+        <v>-0.7574745066705799</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.625989589978158</v>
+        <v>2.399007791013459</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.858618514994656</v>
+        <v>2.859501025412733</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.648686592603032</v>
+        <v>-5.028460441574325</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9987874536396961</v>
+        <v>0.8477604244692554</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3777006576992866</v>
+        <v>-0.7574745066705799</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.631998120375084</v>
+        <v>2.405016321410385</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.937771162786678</v>
+        <v>2.938653673204755</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.500943622368029</v>
+        <v>-4.880717471339323</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.137037289525719</v>
+        <v>0.9860102603552781</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2098933004644035</v>
+        <v>-0.5896671494356968</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.811835182508036</v>
+        <v>2.584853383543337</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.940564784318159</v>
+        <v>2.941447294736236</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.602958304899251</v>
+        <v>-4.982732153870544</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.099025038044712</v>
+        <v>0.9479980088742705</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2098933004644035</v>
+        <v>-0.5896671494356968</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.814628804039517</v>
+        <v>2.587647005074818</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.941227132709817</v>
+        <v>2.942109643127894</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.466348960805158</v>
+        <v>-4.846122809776451</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.154331124074007</v>
+        <v>1.003304094903566</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.07328395637031099</v>
+        <v>-0.4530578053416043</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.897256758887631</v>
+        <v>2.670274959922931</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.940307609449928</v>
+        <v>2.941190119868004</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.609114293627808</v>
+        <v>-4.988888142599102</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.096305467685057</v>
+        <v>0.9452784385146162</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2160492891929614</v>
+        <v>-0.5958231381642547</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.810678035934151</v>
+        <v>2.583696236969452</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.006643163246749</v>
+        <v>3.007525673664825</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.546816294851686</v>
+        <v>-4.926590143822979</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.187560220992327</v>
+        <v>1.036533191821886</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2160492891929614</v>
+        <v>-0.5958231381642547</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.877013589730972</v>
+        <v>2.650031790766272</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.715224035636147</v>
+        <v>2.716106546054223</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.345026097186528</v>
+        <v>-4.724799946157821</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9768571724477881</v>
+        <v>0.8258301432773472</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.01803109702380701</v>
+        <v>-0.3978049459951003</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.704405377421863</v>
+        <v>2.477423578457163</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.785514267958322</v>
+        <v>2.786396778376398</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.285135415543935</v>
+        <v>-4.664909264515228</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.071103677427001</v>
+        <v>0.9200766482565599</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.04185958461878647</v>
+        <v>-0.3379142643525068</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.810630018729594</v>
+        <v>2.583648219764894</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.800142004074365</v>
+        <v>2.801024514492442</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.382875960168909</v>
+        <v>-4.762649809140203</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.046635195693054</v>
+        <v>0.8956081665226137</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.02597030648580628</v>
+        <v>-0.353803542485487</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.815724187965849</v>
+        <v>2.58874238900115</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.798677984899037</v>
+        <v>2.799560495317114</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.559213720291838</v>
+        <v>-4.938987569263132</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9746360724685545</v>
+        <v>0.8236090432981136</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1503674536371231</v>
+        <v>-0.5301413026084164</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.708457512716763</v>
+        <v>2.481475713752064</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.797169602938966</v>
+        <v>2.798052113357042</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.558524348130615</v>
+        <v>-4.938298197101909</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9734034393729722</v>
+        <v>0.8223764102025315</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1503674536371231</v>
+        <v>-0.5301413026084164</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.706949130756692</v>
+        <v>2.479967331791993</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.797032470374402</v>
+        <v>2.797914980792478</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.565095313185208</v>
+        <v>-4.944869162156501</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9706379207865714</v>
+        <v>0.8196108916161307</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.156938418691716</v>
+        <v>-0.5367122676630094</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.702869419159372</v>
+        <v>2.475887620194673</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863225</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.797032470374402</v>
+        <v>2.797914980792478</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.557141342890436</v>
+        <v>-4.936915191861729</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9738195089044803</v>
+        <v>0.8227924797340394</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.156938418691716</v>
+        <v>-0.5367122676630094</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.702869419159372</v>
+        <v>2.475887620194673</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947584</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.803414227402206</v>
+        <v>2.804296737820283</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.656098762742046</v>
+        <v>-4.993842683293693</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9406182979916407</v>
+        <v>0.8064032401890586</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.2558958385433271</v>
+        <v>-0.5936397590949729</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.64987672427621</v>
+        <v>2.448112882363299</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.807558196848483</v>
+        <v>3.474410200955446</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.842142479228222</v>
+        <v>2.682326388821532</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.656098762742046</v>
+        <v>-4.868195611846763</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9406182979916407</v>
+        <v>0.7346917197690797</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2558958385433271</v>
+        <v>-0.467992687648043</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.83520627621459</v>
+        <v>2.401530776232707</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240529.xlsx
+++ b/tame_output/ON/bt/strategyON_20240529.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>19.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,17 +839,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-43.4%</t>
+          <t>-29.1%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.4%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.3%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.0%</t>
+          <t>444.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-648.4%</t>
+          <t>-628.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.7%</t>
+          <t>-38.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-87.8%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-302.8%</t>
+          <t>-280.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-25.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.9%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-150.5%</t>
+          <t>-139.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-270.8%</t>
+          <t>-235.7%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-28.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-205.9%</t>
+          <t>-170.5%</t>
         </is>
       </c>
     </row>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831155</v>
+        <v>3.320996253831154</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355691</v>
+        <v>3.31188830135569</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279816</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511407</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386097</v>
+        <v>3.376932391386095</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998565</v>
+        <v>3.367370539998563</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082129</v>
+        <v>3.299560092082127</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757927</v>
+        <v>3.293490533757924</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760745</v>
+        <v>3.293766719760742</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706675</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296842</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201492</v>
+        <v>3.295507330201489</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.25879198115301</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.20236480037465</v>
+        <v>-10.0244186870167</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9211279962305028</v>
+        <v>-0.8499495508873229</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.438438339951186</v>
+        <v>-2.260492226593236</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.697111344262393</v>
+        <v>1.803879012277163</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608603</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.37748921776119</v>
+        <v>-10.19954310440324</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9766225424376032</v>
+        <v>-0.9054440970944233</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.61356275733773</v>
+        <v>-2.43561664397978</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.606591914577983</v>
+        <v>1.713359582592753</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410276</v>
+        <v>3.485878594410274</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.61194131177568</v>
+        <v>-10.43399519841773</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.077622544944995</v>
+        <v>-1.006444099601815</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.61356275733773</v>
+        <v>-2.43561664397978</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.599372749676387</v>
+        <v>1.706140417691157</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764401</v>
+        <v>3.480692492764399</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.89974515631292</v>
+        <v>-10.72179904295497</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.199416273533867</v>
+        <v>-1.128237828190687</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.901366601874968</v>
+        <v>-2.723420488517018</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.420018252180068</v>
+        <v>1.526785920194838</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.49371601439059</v>
+        <v>3.493716014390588</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.95253131191325</v>
+        <v>-10.7745851985553</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.219414945935442</v>
+        <v>-1.148236500592261</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.997042088457365</v>
+        <v>-2.819095975099415</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.363728750069186</v>
+        <v>1.470496418083956</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297404</v>
+        <v>3.492101641297402</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.18456023164951</v>
+        <v>-11.00661411829156</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.309532785200832</v>
+        <v>-1.238354339857651</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.059054785645789</v>
+        <v>-2.881108672287839</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.329214860385247</v>
+        <v>1.435982528400017</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322548</v>
+        <v>3.573674025322546</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.1325447176807</v>
+        <v>-10.95459860432275</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.284736243926905</v>
+        <v>-1.213557798583725</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.059054785645789</v>
+        <v>-2.881108672287839</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.333205196071648</v>
+        <v>1.439972864086418</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158926</v>
+        <v>3.600038265158924</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.27421655940482</v>
+        <v>-11.09627044604687</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.342880207515295</v>
+        <v>-1.271701762172115</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.059054785645789</v>
+        <v>-2.881108672287839</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.331729969172906</v>
+        <v>1.438497637187676</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.22462571497998</v>
+        <v>-11.04667960162203</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.307990459580489</v>
+        <v>-1.236812014237309</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.009463941220955</v>
+        <v>-2.831517827863005</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.376537885992679</v>
+        <v>1.483305554007449</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.02547360774288</v>
+        <v>-10.84752749438493</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.241380750332332</v>
+        <v>-1.170202304989152</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.844141415271142</v>
+        <v>-2.666195301913191</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.462680267915884</v>
+        <v>1.569447935930654</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.79962845502347</v>
+        <v>-10.62168234166552</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.14146361620836</v>
+        <v>-1.070285170865179</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.802214739683978</v>
+        <v>-2.624268626326028</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.49741534630439</v>
+        <v>1.60418301431916</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.67504979868588</v>
+        <v>-10.49710368532793</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.090493009117264</v>
+        <v>-1.019314563774083</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.802214739683978</v>
+        <v>-2.624268626326028</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.498554490860449</v>
+        <v>1.605322158875219</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.72794508673017</v>
+        <v>-10.54999897337222</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.109017350172871</v>
+        <v>-1.037838904829691</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.797259393595532</v>
+        <v>-2.619313280237582</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.504161472675625</v>
+        <v>1.610929140690395</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.44403635580142</v>
+        <v>-10.26609024244347</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9897201535627351</v>
+        <v>-0.9185417082195544</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.797259393595532</v>
+        <v>-2.619313280237582</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.509895176914261</v>
+        <v>1.616662844929031</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.37266996319177</v>
+        <v>-10.19472384983382</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9709108589127418</v>
+        <v>-0.899732413569561</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.725893000985884</v>
+        <v>-2.547946887627934</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.542977750086185</v>
+        <v>1.649745418100955</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.1088330959877</v>
+        <v>-9.930886982629751</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8752595933440213</v>
+        <v>-0.8040811480008405</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.725893000985884</v>
+        <v>-2.547946887627934</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.533094268773277</v>
+        <v>1.639861936788047</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.841591295119304</v>
+        <v>-9.663645181761353</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7701974334960355</v>
+        <v>-0.6990189881528552</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.725893000985884</v>
+        <v>-2.547946887627934</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.531259708273903</v>
+        <v>1.638027376288673</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.743684256442814</v>
+        <v>-9.565738143084863</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7313349329989003</v>
+        <v>-0.66015648765572</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.657907251125327</v>
+        <v>-2.479961137767377</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.571750843216776</v>
+        <v>1.678518511231546</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.719730715466856</v>
+        <v>-9.541784602108905</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7210850104630233</v>
+        <v>-0.649906565119843</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.63395371014937</v>
+        <v>-2.45600759679142</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.586791473947845</v>
+        <v>1.693559141962615</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.455670777144059</v>
+        <v>-9.277724663786108</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6287213512956571</v>
+        <v>-0.5575429059524764</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.369893771826574</v>
+        <v>-2.191947658468624</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.73196712077977</v>
+        <v>1.83873478879454</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.748591153639222</v>
+        <v>-8.570645040281271</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3486765355540227</v>
+        <v>-0.2774980902108424</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.369893771826574</v>
+        <v>-2.191947658468624</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.729180087119469</v>
+        <v>1.835947755134239</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.708406855273031</v>
+        <v>-8.53046074191508</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3322591923197051</v>
+        <v>-0.2610807469765248</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.329709473460383</v>
+        <v>-2.151763360102433</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.753634290027025</v>
+        <v>1.860401958041795</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.628337059735227</v>
+        <v>-8.450390946377276</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3008644528838267</v>
+        <v>-0.2296860075406464</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.249639677922579</v>
+        <v>-2.071693564564629</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.801042988570464</v>
+        <v>1.907810656585234</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.394855837505627</v>
+        <v>-8.216909724147676</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1995475351541343</v>
+        <v>-0.128369089810954</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.016158455692981</v>
+        <v>-1.838212342335031</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.949056150746076</v>
+        <v>2.055823818760846</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.245189446498113</v>
+        <v>-8.067243333140162</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.142573189064088</v>
+        <v>-0.07139474372090771</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.923254964450445</v>
+        <v>-1.745308851092495</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.001906035178638</v>
+        <v>2.108673703193408</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.135382208123158</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.209951890223268</v>
+        <v>-7.934967859509276</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1489549722798964</v>
+        <v>-0.02311706752152576</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.888017408175599</v>
+        <v>-1.613033377461608</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.002571763217799</v>
+        <v>2.183406474118967</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105955</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.138197268810795</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.019352215550114</v>
+        <v>-7.744368184836123</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.06990004172299802</v>
+        <v>0.05593786303537174</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.697417733502446</v>
+        <v>-1.422433702788455</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.119746628709327</v>
+        <v>2.300581339610495</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75388257196099</v>
+        <v>3.753882571960989</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.151103610034454</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.770352416866533</v>
+        <v>-7.495368386152542</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.04260621897409278</v>
+        <v>0.168444123732463</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.697417733502446</v>
+        <v>-1.422433702788455</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.132652969932987</v>
+        <v>2.313487680834154</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.023127680435235</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.875942406639638</v>
+        <v>-7.600958375925646</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1276057065343674</v>
+        <v>-0.001767801775997668</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.80300772327555</v>
+        <v>-1.528023692561559</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.941323046469905</v>
+        <v>2.122157757371073</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.071672022312321</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.894677308758235</v>
+        <v>-7.619693278044243</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.08655532550471978</v>
+        <v>0.03928257925364997</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.80300772327555</v>
+        <v>-1.528023692561559</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.989867388346991</v>
+        <v>2.170702099248159</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.951793099624154</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.746737267350635</v>
+        <v>-7.471753236636644</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1472582316298476</v>
+        <v>-0.02142032687147788</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.782686807366993</v>
+        <v>-1.507702776653002</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.882181015203958</v>
+        <v>2.063015726105126</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.943079113370676</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.729579117219341</v>
+        <v>-7.45459508650535</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1491089578308085</v>
+        <v>-0.02327105307243826</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.765528657235699</v>
+        <v>-1.490544626521707</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.883761919029257</v>
+        <v>2.064596629930425</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.936118501275582</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.686030710448651</v>
+        <v>-7.411046679734659</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1386502072176254</v>
+        <v>-0.01281230245925524</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.765528657235699</v>
+        <v>-1.490544626521707</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.876801306934164</v>
+        <v>2.057636017835332</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.950580855656725</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.443882316994793</v>
+        <v>-7.168898286280801</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.02732849545493909</v>
+        <v>0.09850940930343111</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.765528657235699</v>
+        <v>-1.490544626521707</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.891263661315307</v>
+        <v>2.072098372216475</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.94511297611592</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.380652945226444</v>
+        <v>-7.105668914512453</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.007504626288404648</v>
+        <v>0.1183332784699656</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.765528657235699</v>
+        <v>-1.490544626521707</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.885795781774502</v>
+        <v>2.06663049267567</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.942611070126497</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.257361810409313</v>
+        <v>-6.982377779695322</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.03930992164902447</v>
+        <v>0.1651478264073947</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.642237522418568</v>
+        <v>-1.367253491704577</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.957268556675357</v>
+        <v>2.138103267576525</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919912</v>
+        <v>3.812453678919909</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.950312048363823</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.23621261150587</v>
+        <v>-6.961228580791879</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.05547057944772726</v>
+        <v>0.181308484206097</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.621088323515125</v>
+        <v>-1.346104292801134</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.977659054254748</v>
+        <v>2.158493765155916</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318097</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.946092756710873</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.992447169522426</v>
+        <v>-6.717463138808434</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1487574645881558</v>
+        <v>0.2745953693465255</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.621088323515125</v>
+        <v>-1.346104292801134</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.973439762601799</v>
+        <v>2.154274473502967</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057528</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.948217070630889</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.845550141804555</v>
+        <v>-6.570566111090564</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2096405895953199</v>
+        <v>0.3354784943536897</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.573430081536537</v>
+        <v>-1.298446050822545</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.004159021708968</v>
+        <v>2.184993732610136</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.940959145614591</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.59569974785548</v>
+        <v>-6.320715717141489</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.302322822158652</v>
+        <v>0.4281607269170218</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.573430081536537</v>
+        <v>-1.298446050822545</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.99690109669267</v>
+        <v>2.177735807593838</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.94455826913524</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.419807655388048</v>
+        <v>-6.144823624674057</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3762787826662732</v>
+        <v>0.5021166874246434</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.573430081536537</v>
+        <v>-1.298446050822545</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.000500220213318</v>
+        <v>2.181334931114487</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.957885775189794</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.248361192365585</v>
+        <v>-5.973377161651594</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4581848739298127</v>
+        <v>0.5840227786881824</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.401983618514074</v>
+        <v>-1.126999587800082</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.11669560408135</v>
+        <v>2.297530314982518</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.956906252806091</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.023328192696762</v>
+        <v>-5.748344161982771</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5472185514136387</v>
+        <v>0.6730564561720089</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.176950618845251</v>
+        <v>-0.9019665881312596</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.250735881498941</v>
+        <v>2.431570592400109</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.961601053860408</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.959692450462827</v>
+        <v>-5.684708419748836</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5773676493615296</v>
+        <v>0.7032055541198998</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.113314876611316</v>
+        <v>-0.8383308458973251</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.293612127893619</v>
+        <v>2.474446838794787</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.942795312644204</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.866692409256929</v>
+        <v>-5.591708378542938</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5957619246276846</v>
+        <v>0.7215998293860548</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.113314876611316</v>
+        <v>-0.8383308458973251</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.274806386677414</v>
+        <v>2.455641097578583</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.79769488424229</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.944538389269081</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.626261912452069</v>
+        <v>-5.351277881738078</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6936771999745064</v>
+        <v>0.8195151047328761</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8728843798064561</v>
+        <v>-0.5979003490924648</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.420807761385208</v>
+        <v>2.601642472286376</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.948467703103901</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.554019344280874</v>
+        <v>-5.279035313566883</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7265035410778045</v>
+        <v>0.8523414458361742</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8728843798064561</v>
+        <v>-0.5979003490924648</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.424737075220028</v>
+        <v>2.605571786121196</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.949146287021241</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.501021021999486</v>
+        <v>-5.226036991285495</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7483814539076996</v>
+        <v>0.8742193586660694</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8175481208045172</v>
+        <v>-0.542564090090526</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.458617414538531</v>
+        <v>2.639452125439699</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.946144358241235</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.392216136519759</v>
+        <v>-5.117232105805768</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7889014793195837</v>
+        <v>0.9147393840779539</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8175481208045172</v>
+        <v>-0.542564090090526</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.455615485758525</v>
+        <v>2.636450196659693</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.947723395251849</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.172195338482749</v>
+        <v>-4.897211307768758</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.878488835545002</v>
+        <v>1.004326740303372</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.676328275736537</v>
+        <v>-0.4013442450225457</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.541926429809927</v>
+        <v>2.722761140711095</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.963617578053672</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.039327649419471</v>
+        <v>-4.76434361870548</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9475300939721363</v>
+        <v>1.073367998730506</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.676328275736537</v>
+        <v>-0.4013442450225457</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.55782061261175</v>
+        <v>2.738655323512919</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.964763422493974</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.879812545900101</v>
+        <v>-4.60482851518611</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.012481979820186</v>
+        <v>1.138319884578556</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.516813172217167</v>
+        <v>-0.2418291415031758</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.654675519163674</v>
+        <v>2.835510230064842</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.974851525055414</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.735140400800364</v>
+        <v>-4.460156370086373</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.080438940421521</v>
+        <v>1.206276845179891</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3721410271174296</v>
+        <v>-0.09715699640343839</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.751566908784957</v>
+        <v>2.932401619686125</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.96088901645684</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.795015228158056</v>
+        <v>-4.520031197444065</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.04252650087987</v>
+        <v>1.16836440563824</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4320158544751218</v>
+        <v>-0.1570318237611305</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.701679503771767</v>
+        <v>2.882514214672935</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674518</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.983289509779406</v>
+        <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.708215730379047</v>
+        <v>-4.433231699665056</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.09964679331404</v>
+        <v>1.22548469807241</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4320158544751218</v>
+        <v>-0.1570318237611305</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.724079997094333</v>
+        <v>2.904914707995502</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.983361911152818</v>
+        <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.710685436840853</v>
+        <v>-4.435701406126862</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.09873131210273</v>
+        <v>1.2245692168611</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4344855609369279</v>
+        <v>-0.1595015302229367</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.722670574590662</v>
+        <v>2.90350528549183</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.99436883362752</v>
+        <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.779055623164863</v>
+        <v>-4.504071592450872</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.082390160047827</v>
+        <v>1.208228064806197</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.425209861900713</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.739242916487092</v>
+        <v>2.920077627388261</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.984805542259411</v>
+        <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.887593804080997</v>
+        <v>-4.612609773367006</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.029411596313265</v>
+        <v>1.155249501071635</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.425209861900713</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.729679625118984</v>
+        <v>2.910514336020152</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.809515107299798</v>
+        <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.918586963409703</v>
+        <v>-4.643602932695711</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8417238976221699</v>
+        <v>0.9675618023805399</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.425209861900713</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.55438919015937</v>
+        <v>2.735223901060539</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.814082339291586</v>
+        <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.743112703617234</v>
+        <v>-4.468128672903243</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9164808335309451</v>
+        <v>1.042318738289315</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.425209861900713</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.558956422151158</v>
+        <v>2.739791133052327</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.789824368052793</v>
+        <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.854048956258483</v>
+        <v>-4.579064925544492</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8478483612356527</v>
+        <v>0.9736862659940226</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.425209861900713</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.534698450912365</v>
+        <v>2.715533161813534</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.792955753272699</v>
+        <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.057075533801716</v>
+        <v>-4.782091503087725</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7697691154382649</v>
+        <v>0.8956070201966349</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6282364394439464</v>
+        <v>-0.3532524087299551</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.416013889606331</v>
+        <v>2.596848600507499</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.803128139704831</v>
+        <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.899149934866423</v>
+        <v>-4.624165904152432</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8431117414445144</v>
+        <v>0.9689496462028844</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6282364394439464</v>
+        <v>-0.3532524087299551</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.426186276038463</v>
+        <v>2.607020986939632</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.798074410278691</v>
+        <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.812906471840045</v>
+        <v>-4.537922441126054</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8725553972289259</v>
+        <v>0.9983933019872959</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6282364394439464</v>
+        <v>-0.3532524087299551</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.421132546612323</v>
+        <v>2.601967257513492</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.789850185723217</v>
+        <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.858213291239025</v>
+        <v>-4.583229260525034</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8462084449138594</v>
+        <v>0.9720463496722296</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6690466024531772</v>
+        <v>-0.3940625717391859</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.388422224251311</v>
+        <v>2.569256935152479</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.790402058756318</v>
+        <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.735085584244942</v>
+        <v>-4.612262365227335</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8960114007445943</v>
+        <v>0.9609849808244106</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6690466024531772</v>
+        <v>-0.3940625717391859</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.388974097284412</v>
+        <v>2.569808808185581</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.719674750647684</v>
+        <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.642275102794082</v>
+        <v>-4.519451883776475</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8624082852163037</v>
+        <v>0.9273818652961201</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.5762361210023178</v>
+        <v>-0.3012520902883266</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.373933078046293</v>
+        <v>2.554767788947462</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.721548226572285</v>
+        <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.593712050573052</v>
+        <v>-4.470888831555445</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8837069820293166</v>
+        <v>0.948680562109133</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.5276730687812876</v>
+        <v>-0.2526890380672964</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.404944385303513</v>
+        <v>2.585779096204681</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.716623935084008</v>
+        <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.481040832336802</v>
+        <v>-4.358217613319195</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9238511778355396</v>
+        <v>0.988824757915356</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.4150018505450374</v>
+        <v>-0.1400178198310462</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.467622824756986</v>
+        <v>2.648457535658154</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.722115230914675</v>
+        <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.368663831154129</v>
+        <v>-4.245840612136522</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.974293274139276</v>
+        <v>1.039266854219092</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.4150018505450374</v>
+        <v>-0.1400178198310462</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.473114120587653</v>
+        <v>2.653948831488821</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498861</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.733612432683214</v>
+        <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.56689840004086</v>
+        <v>-4.444075181023253</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9064966483531227</v>
+        <v>0.9714702284329391</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.613236419431768</v>
+        <v>-0.3382523887177767</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.365670581024153</v>
+        <v>2.546505291925322</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705321</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.571968152683867</v>
+        <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.649899681066139</v>
+        <v>-4.527076462048532</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7116518559436644</v>
+        <v>0.7766254360234808</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.6318073039589418</v>
+        <v>-0.3568232732449505</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.192883770308502</v>
+        <v>2.373718481209671</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729265</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.692117813403073</v>
+        <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.776966687373127</v>
+        <v>-4.65414346835552</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7809747141400749</v>
+        <v>0.8459482942198913</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.6318073039589418</v>
+        <v>-0.3568232732449505</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.313033431027708</v>
+        <v>2.493868141928877</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.733012441190763</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.706630839505396</v>
+        <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.86356527035423</v>
+        <v>-4.740742051336623</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7608483070499568</v>
+        <v>0.8258218871297731</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.6318073039589418</v>
+        <v>-0.3568232732449505</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.327546457130031</v>
+        <v>2.5083811680312</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913421</v>
+        <v>3.741174069913419</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.704050280847765</v>
+        <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.825181607796079</v>
+        <v>-4.702358388778472</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7736212134155858</v>
+        <v>0.8385947934954021</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.5934236414007906</v>
+        <v>-0.3184396106867993</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.347996096007291</v>
+        <v>2.528830806908459</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.75114719753248</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.700779309693067</v>
+        <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.648065277760913</v>
+        <v>-4.525242058743306</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8411967742749542</v>
+        <v>0.9061703543547706</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.5934236414007906</v>
+        <v>-0.3184396106867993</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.344725124852593</v>
+        <v>2.525559835753761</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793898</v>
+        <v>3.741328448793896</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.70146270145498</v>
+        <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.618363153784619</v>
+        <v>-4.495539934767012</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8537610156273847</v>
+        <v>0.9187345957072011</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.5978937666161039</v>
+        <v>-0.3229097359021127</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.342726441485318</v>
+        <v>2.523561152386486</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011229</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.695249676761394</v>
+        <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.438987732545852</v>
+        <v>-4.316164513528244</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9192981594293061</v>
+        <v>0.9842717395091225</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.4411170084453853</v>
+        <v>-0.166132977731394</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.430579471694163</v>
+        <v>2.611414182595332</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.676057132092984</v>
+        <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.484001946066458</v>
+        <v>-4.36117872704885</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8820999293526532</v>
+        <v>0.94707350943247</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.4714659037599899</v>
+        <v>-0.1964818730459986</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.39317758983699</v>
+        <v>2.574012300738159</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509531</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.68174869443193</v>
+        <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.751006456338893</v>
+        <v>-4.628183237321285</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.780989687582625</v>
+        <v>0.8459632676624418</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.6658289418029384</v>
+        <v>-0.3908449110889472</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.282251329350167</v>
+        <v>2.463086040251335</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.702309454760806</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.680952616328431</v>
+        <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.852204237776066</v>
+        <v>-4.729381018758458</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7397144969042573</v>
+        <v>0.8046880769840741</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.7342377553482575</v>
+        <v>-0.4592537246342664</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.240409963119477</v>
+        <v>2.421244674020645</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815452</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.678552577882748</v>
+        <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.819728651605294</v>
+        <v>-4.696905432587686</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7503046929268828</v>
+        <v>0.8152782730066996</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.7342377553482575</v>
+        <v>-0.4592537246342664</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.238009924673793</v>
+        <v>2.418844635574962</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378103</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.675077297090993</v>
+        <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.800690523897996</v>
+        <v>-4.677867304880388</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7544446632180468</v>
+        <v>0.8194182432978634</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.7924213666794521</v>
+        <v>-0.5174373359654609</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.199624477083322</v>
+        <v>2.38045918798449</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.852659166029673</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.831817155048615</v>
+        <v>-4.708993936031007</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9195758796964799</v>
+        <v>0.9845494597762967</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.7924213666794521</v>
+        <v>-0.5174373359654609</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.377206346022002</v>
+        <v>2.55804105692317</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.853492495015807</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.884137535649407</v>
+        <v>-4.761314316631799</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8994810564422968</v>
+        <v>0.9644546365221136</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.7574745066705799</v>
+        <v>-0.4824904759565888</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.399007791013459</v>
+        <v>2.579842501914627</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789119</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.859501025412733</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.028460441574325</v>
+        <v>-4.905637222556718</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8477604244692554</v>
+        <v>0.9127340045490719</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.7574745066705799</v>
+        <v>-0.4824904759565888</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.405016321410385</v>
+        <v>2.585851032311553</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519904</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.938653673204755</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.880717471339323</v>
+        <v>-4.757894252321715</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9860102603552781</v>
+        <v>1.050983840435095</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.5896671494356968</v>
+        <v>-0.3146831187217056</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.584853383543337</v>
+        <v>2.765688094444505</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.941447294736236</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.982732153870544</v>
+        <v>-4.859908934852936</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9479980088742705</v>
+        <v>1.012971588954087</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.5896671494356968</v>
+        <v>-0.3146831187217056</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.587647005074818</v>
+        <v>2.768481715975986</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.942109643127894</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.846122809776451</v>
+        <v>-4.723299590758844</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.003304094903566</v>
+        <v>1.068277674983383</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4530578053416043</v>
+        <v>-0.1780737746276131</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.670274959922931</v>
+        <v>2.8511096708241</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.941190119868004</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.988888142599102</v>
+        <v>-4.866064923581494</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9452784385146162</v>
+        <v>1.010252018594433</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.5958231381642547</v>
+        <v>-0.3208391074502636</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.583696236969452</v>
+        <v>2.76453094787062</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.007525673664825</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.926590143822979</v>
+        <v>-4.803766924805371</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.036533191821886</v>
+        <v>1.101506771901703</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.5958231381642547</v>
+        <v>-0.3208391074502636</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.650031790766272</v>
+        <v>2.830866501667441</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992186</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.716106546054223</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.724799946157821</v>
+        <v>-4.601976727140213</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8258301432773472</v>
+        <v>0.890803723357164</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.3978049459951003</v>
+        <v>-0.1228209152811092</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.477423578457163</v>
+        <v>2.658258289358332</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.786396778376398</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.664909264515228</v>
+        <v>-4.54208604549762</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9200766482565599</v>
+        <v>0.9850502283363765</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.3379142643525068</v>
+        <v>-0.06293023363851569</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.583648219764894</v>
+        <v>2.764482930666063</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319541</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.801024514492442</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.762649809140203</v>
+        <v>-4.639826590122595</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8956081665226137</v>
+        <v>0.9605817466024305</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.353803542485487</v>
+        <v>-0.07881951177149588</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.58874238900115</v>
+        <v>2.769577099902318</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.799560495317114</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.938987569263132</v>
+        <v>-4.816164350245524</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8236090432981136</v>
+        <v>0.8885826233779304</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.5301413026084164</v>
+        <v>-0.2551572718944253</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.481475713752064</v>
+        <v>2.662310424653232</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397789</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.798052113357042</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.938298197101909</v>
+        <v>-4.815474978084301</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8223764102025315</v>
+        <v>0.8873499902823481</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.5301413026084164</v>
+        <v>-0.2551572718944253</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.479967331791993</v>
+        <v>2.660802042693161</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.836023391024957</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.797914980792478</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.944869162156501</v>
+        <v>-4.822045943138893</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8196108916161307</v>
+        <v>0.8845844716959472</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.5367122676630094</v>
+        <v>-0.2617282369490182</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.475887620194673</v>
+        <v>2.656722331095841</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863221</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.797914980792478</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.936915191861729</v>
+        <v>-4.814091972844121</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8227924797340394</v>
+        <v>0.8877660598138561</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.5367122676630094</v>
+        <v>-0.2617282369490182</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.475887620194673</v>
+        <v>2.656722331095841</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947584</v>
+        <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.804296737820283</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.993842683293693</v>
+        <v>-4.803718596511034</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8064032401890586</v>
+        <v>0.8982971673748956</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.5936397590949729</v>
+        <v>-0.2513548606159309</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.448112882363299</v>
+        <v>2.669328113923498</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.474410200955446</v>
+        <v>3.471841531545086</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.682326388821532</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.868195611846763</v>
+        <v>-4.669211775459552</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7346917197690797</v>
+        <v>0.9569922691702131</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.467992687648043</v>
+        <v>-0.1168480395644488</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.401530776232707</v>
+        <v>2.754924579929112</v>
       </c>
     </row>
   </sheetData>
